--- a/research/traditional_assets/database/data/norway/norway_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_auto_parts.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09736887025547922</v>
+        <v>0.09718975874091716</v>
       </c>
       <c r="C2">
-        <v>333.8221180892392</v>
+        <v>330.8733186889745</v>
       </c>
       <c r="D2">
-        <v>244.2221180892392</v>
+        <v>245.0733186889745</v>
       </c>
       <c r="E2">
-        <v>-222.4</v>
+        <v>-218.6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="G2">
         <v>89.59999999999999</v>
@@ -1445,28 +1445,28 @@
         <v>18.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.19114</v>
       </c>
       <c r="N2">
-        <v>18.6</v>
+        <v>18.40886</v>
       </c>
       <c r="O2">
-        <v>4.092000000000001</v>
+        <v>4.0499492</v>
       </c>
       <c r="P2">
-        <v>14.508</v>
+        <v>14.3589108</v>
       </c>
       <c r="Q2">
-        <v>47.408</v>
+        <v>47.2589108</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09736887025547922</v>
+        <v>0.09777517044537087</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.200350356706025</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>97.31087161243067</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09718975874091716</v>
+        <v>0.09701064722635512</v>
       </c>
       <c r="C3">
-        <v>330.8733186889745</v>
+        <v>327.9304735125623</v>
       </c>
       <c r="D3">
-        <v>245.0733186889745</v>
+        <v>245.9304735125624</v>
       </c>
       <c r="E3">
-        <v>-218.6</v>
+        <v>-214.8</v>
       </c>
       <c r="F3">
-        <v>3.8</v>
+        <v>7.600000000000001</v>
       </c>
       <c r="G3">
         <v>89.59999999999999</v>
@@ -1527,28 +1527,28 @@
         <v>18.6</v>
       </c>
       <c r="M3">
-        <v>0.19114</v>
+        <v>0.38228</v>
       </c>
       <c r="N3">
-        <v>18.40886</v>
+        <v>18.21772</v>
       </c>
       <c r="O3">
-        <v>4.0499492</v>
+        <v>4.0078984</v>
       </c>
       <c r="P3">
-        <v>14.3589108</v>
+        <v>14.2098216</v>
       </c>
       <c r="Q3">
-        <v>47.2589108</v>
+        <v>47.1098216</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09777517044537087</v>
+        <v>0.09818976247587258</v>
       </c>
       <c r="T3">
-        <v>1.200350356706025</v>
+        <v>1.209925230389667</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>97.31087161243067</v>
+        <v>48.65543580621534</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09701064722635512</v>
+        <v>0.09683153571179307</v>
       </c>
       <c r="C4">
-        <v>327.9304735125623</v>
+        <v>324.9936452547684</v>
       </c>
       <c r="D4">
-        <v>245.9304735125624</v>
+        <v>246.7936452547684</v>
       </c>
       <c r="E4">
-        <v>-214.8</v>
+        <v>-211</v>
       </c>
       <c r="F4">
-        <v>7.600000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="G4">
         <v>89.59999999999999</v>
@@ -1609,28 +1609,28 @@
         <v>18.6</v>
       </c>
       <c r="M4">
-        <v>0.38228</v>
+        <v>0.57342</v>
       </c>
       <c r="N4">
-        <v>18.21772</v>
+        <v>18.02658</v>
       </c>
       <c r="O4">
-        <v>4.0078984</v>
+        <v>3.9658476</v>
       </c>
       <c r="P4">
-        <v>14.2098216</v>
+        <v>14.0607324</v>
       </c>
       <c r="Q4">
-        <v>47.1098216</v>
+        <v>46.9607324</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09818976247587258</v>
+        <v>0.09861290279566295</v>
       </c>
       <c r="T4">
-        <v>1.209925230389667</v>
+        <v>1.21969752414926</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.65543580621534</v>
+        <v>32.43695720414357</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09683153571179307</v>
+        <v>0.09665242419723101</v>
       </c>
       <c r="C5">
-        <v>324.9936452547684</v>
+        <v>322.0628974936475</v>
       </c>
       <c r="D5">
-        <v>246.7936452547684</v>
+        <v>247.6628974936475</v>
       </c>
       <c r="E5">
-        <v>-211</v>
+        <v>-207.2</v>
       </c>
       <c r="F5">
-        <v>11.4</v>
+        <v>15.2</v>
       </c>
       <c r="G5">
         <v>89.59999999999999</v>
@@ -1691,28 +1691,28 @@
         <v>18.6</v>
       </c>
       <c r="M5">
-        <v>0.57342</v>
+        <v>0.76456</v>
       </c>
       <c r="N5">
-        <v>18.02658</v>
+        <v>17.83544</v>
       </c>
       <c r="O5">
-        <v>3.9658476</v>
+        <v>3.9237968</v>
       </c>
       <c r="P5">
-        <v>14.0607324</v>
+        <v>13.9116432</v>
       </c>
       <c r="Q5">
-        <v>46.9607324</v>
+        <v>46.8116432</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09861290279566295</v>
+        <v>0.0990448585387823</v>
       </c>
       <c r="T5">
-        <v>1.21969752414926</v>
+        <v>1.229673407362178</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.43695720414357</v>
+        <v>24.32771790310767</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09665242419723101</v>
+        <v>0.09647331268266895</v>
       </c>
       <c r="C6">
-        <v>322.0628974936475</v>
+        <v>319.1382947061547</v>
       </c>
       <c r="D6">
-        <v>247.6628974936475</v>
+        <v>248.5382947061547</v>
       </c>
       <c r="E6">
-        <v>-207.2</v>
+        <v>-203.4</v>
       </c>
       <c r="F6">
-        <v>15.2</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>89.59999999999999</v>
@@ -1773,28 +1773,28 @@
         <v>18.6</v>
       </c>
       <c r="M6">
-        <v>0.76456</v>
+        <v>0.9557</v>
       </c>
       <c r="N6">
-        <v>17.83544</v>
+        <v>17.6443</v>
       </c>
       <c r="O6">
-        <v>3.9237968</v>
+        <v>3.881746</v>
       </c>
       <c r="P6">
-        <v>13.9116432</v>
+        <v>13.762554</v>
       </c>
       <c r="Q6">
-        <v>46.8116432</v>
+        <v>46.662554</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0990448585387823</v>
+        <v>0.09948590808701996</v>
       </c>
       <c r="T6">
-        <v>1.229673407362178</v>
+        <v>1.239859309169052</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.32771790310767</v>
+        <v>19.46217432248614</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09647331268266895</v>
+        <v>0.0962942011681069</v>
       </c>
       <c r="C7">
-        <v>319.1382947061547</v>
+        <v>316.2199022840879</v>
       </c>
       <c r="D7">
-        <v>248.5382947061547</v>
+        <v>249.4199022840879</v>
       </c>
       <c r="E7">
-        <v>-203.4</v>
+        <v>-199.6</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>22.8</v>
       </c>
       <c r="G7">
         <v>89.59999999999999</v>
@@ -1855,28 +1855,28 @@
         <v>18.6</v>
       </c>
       <c r="M7">
-        <v>0.9557</v>
+        <v>1.14684</v>
       </c>
       <c r="N7">
-        <v>17.6443</v>
+        <v>17.45316</v>
       </c>
       <c r="O7">
-        <v>3.881746</v>
+        <v>3.8396952</v>
       </c>
       <c r="P7">
-        <v>13.762554</v>
+        <v>13.6134648</v>
       </c>
       <c r="Q7">
-        <v>46.662554</v>
+        <v>46.5134648</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09948590808701996</v>
+        <v>0.09993634166819883</v>
       </c>
       <c r="T7">
-        <v>1.239859309169052</v>
+        <v>1.250261932290966</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.46217432248614</v>
+        <v>16.21847860207178</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0962942011681069</v>
+        <v>0.09611508965354484</v>
       </c>
       <c r="C8">
-        <v>316.2199022840879</v>
+        <v>313.3077865503714</v>
       </c>
       <c r="D8">
-        <v>249.4199022840879</v>
+        <v>250.3077865503714</v>
       </c>
       <c r="E8">
-        <v>-199.6</v>
+        <v>-195.8</v>
       </c>
       <c r="F8">
-        <v>22.8</v>
+        <v>26.6</v>
       </c>
       <c r="G8">
         <v>89.59999999999999</v>
@@ -1937,28 +1937,28 @@
         <v>18.6</v>
       </c>
       <c r="M8">
-        <v>1.14684</v>
+        <v>1.33798</v>
       </c>
       <c r="N8">
-        <v>17.45316</v>
+        <v>17.26202</v>
       </c>
       <c r="O8">
-        <v>3.8396952</v>
+        <v>3.797644400000001</v>
       </c>
       <c r="P8">
-        <v>13.6134648</v>
+        <v>13.4643756</v>
       </c>
       <c r="Q8">
-        <v>46.5134648</v>
+        <v>46.3643756</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09993634166819883</v>
+        <v>0.100396461993059</v>
       </c>
       <c r="T8">
-        <v>1.250261932290966</v>
+        <v>1.260888267738082</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.21847860207178</v>
+        <v>13.9015530874901</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09611508965354486</v>
+        <v>0.0960295781389828</v>
       </c>
       <c r="C9">
-        <v>313.3077865503712</v>
+        <v>309.9339139185004</v>
       </c>
       <c r="D9">
-        <v>250.3077865503713</v>
+        <v>250.7339139185004</v>
       </c>
       <c r="E9">
-        <v>-195.8</v>
+        <v>-192</v>
       </c>
       <c r="F9">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
       <c r="G9">
         <v>89.59999999999999</v>
@@ -2019,45 +2019,45 @@
         <v>18.6</v>
       </c>
       <c r="M9">
-        <v>1.33798</v>
+        <v>1.57472</v>
       </c>
       <c r="N9">
-        <v>17.26202</v>
+        <v>17.02528</v>
       </c>
       <c r="O9">
-        <v>3.7976444</v>
+        <v>3.745561600000001</v>
       </c>
       <c r="P9">
-        <v>13.4643756</v>
+        <v>13.2797184</v>
       </c>
       <c r="Q9">
-        <v>46.3643756</v>
+        <v>46.1797184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.100396461993059</v>
+        <v>0.100866584933677</v>
       </c>
       <c r="T9">
-        <v>1.260888267738083</v>
+        <v>1.271745610477528</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.9015530874901</v>
+        <v>11.81162365372892</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0960295781389828</v>
+        <v>0.09586216662442075</v>
       </c>
       <c r="C10">
-        <v>309.9339139185004</v>
+        <v>306.972386304166</v>
       </c>
       <c r="D10">
-        <v>250.7339139185004</v>
+        <v>251.572386304166</v>
       </c>
       <c r="E10">
-        <v>-192</v>
+        <v>-188.2</v>
       </c>
       <c r="F10">
-        <v>30.4</v>
+        <v>34.2</v>
       </c>
       <c r="G10">
         <v>89.59999999999999</v>
@@ -2101,28 +2101,28 @@
         <v>18.6</v>
       </c>
       <c r="M10">
-        <v>1.57472</v>
+        <v>1.77156</v>
       </c>
       <c r="N10">
-        <v>17.02528</v>
+        <v>16.82844</v>
       </c>
       <c r="O10">
-        <v>3.745561600000001</v>
+        <v>3.7022568</v>
       </c>
       <c r="P10">
-        <v>13.2797184</v>
+        <v>13.1261832</v>
       </c>
       <c r="Q10">
-        <v>46.1797184</v>
+        <v>46.0261832</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.100866584933677</v>
+        <v>0.1013470402466162</v>
       </c>
       <c r="T10">
-        <v>1.271745610477528</v>
+        <v>1.282841576134323</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.81162365372892</v>
+        <v>10.49922102553682</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09586216662442075</v>
+        <v>0.09582735510985869</v>
       </c>
       <c r="C11">
-        <v>306.972386304166</v>
+        <v>303.347442846132</v>
       </c>
       <c r="D11">
-        <v>251.572386304166</v>
+        <v>251.747442846132</v>
       </c>
       <c r="E11">
-        <v>-188.2</v>
+        <v>-184.4</v>
       </c>
       <c r="F11">
-        <v>34.2</v>
+        <v>38</v>
       </c>
       <c r="G11">
         <v>89.59999999999999</v>
@@ -2183,45 +2183,45 @@
         <v>18.6</v>
       </c>
       <c r="M11">
-        <v>1.77156</v>
+        <v>2.033</v>
       </c>
       <c r="N11">
-        <v>16.82844</v>
+        <v>16.567</v>
       </c>
       <c r="O11">
-        <v>3.7022568</v>
+        <v>3.64474</v>
       </c>
       <c r="P11">
-        <v>13.1261832</v>
+        <v>12.92226</v>
       </c>
       <c r="Q11">
-        <v>46.0261832</v>
+        <v>45.82226</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1013470402466162</v>
+        <v>0.1018381723442874</v>
       </c>
       <c r="T11">
-        <v>1.282841576134323</v>
+        <v>1.294184118805714</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.49922102553682</v>
+        <v>9.149040826364978</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09582735510985869</v>
+        <v>0.09567320359529664</v>
       </c>
       <c r="C12">
-        <v>303.347442846132</v>
+        <v>300.3255610900845</v>
       </c>
       <c r="D12">
-        <v>251.747442846132</v>
+        <v>252.5255610900845</v>
       </c>
       <c r="E12">
-        <v>-184.4</v>
+        <v>-180.6</v>
       </c>
       <c r="F12">
-        <v>38</v>
+        <v>41.8</v>
       </c>
       <c r="G12">
         <v>89.59999999999999</v>
@@ -2265,28 +2265,28 @@
         <v>18.6</v>
       </c>
       <c r="M12">
-        <v>2.033</v>
+        <v>2.2363</v>
       </c>
       <c r="N12">
-        <v>16.567</v>
+        <v>16.3637</v>
       </c>
       <c r="O12">
-        <v>3.64474</v>
+        <v>3.600014</v>
       </c>
       <c r="P12">
-        <v>12.92226</v>
+        <v>12.763686</v>
       </c>
       <c r="Q12">
-        <v>45.82226</v>
+        <v>45.663686</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1018381723442874</v>
+        <v>0.1023403411183108</v>
       </c>
       <c r="T12">
-        <v>1.294184118805714</v>
+        <v>1.305781550076462</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.149040826364978</v>
+        <v>8.317309842149982</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09567320359529664</v>
+        <v>0.09551905208073458</v>
       </c>
       <c r="C13">
-        <v>300.3255610900845</v>
+        <v>297.3085043699455</v>
       </c>
       <c r="D13">
-        <v>252.5255610900845</v>
+        <v>253.3085043699455</v>
       </c>
       <c r="E13">
-        <v>-180.6</v>
+        <v>-176.8</v>
       </c>
       <c r="F13">
-        <v>41.8</v>
+        <v>45.6</v>
       </c>
       <c r="G13">
         <v>89.59999999999999</v>
@@ -2347,28 +2347,28 @@
         <v>18.6</v>
       </c>
       <c r="M13">
-        <v>2.2363</v>
+        <v>2.4396</v>
       </c>
       <c r="N13">
-        <v>16.3637</v>
+        <v>16.1604</v>
       </c>
       <c r="O13">
-        <v>3.600014</v>
+        <v>3.555288</v>
       </c>
       <c r="P13">
-        <v>12.763686</v>
+        <v>12.605112</v>
       </c>
       <c r="Q13">
-        <v>45.663686</v>
+        <v>45.505112</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1023403411183108</v>
+        <v>0.1028539228190166</v>
       </c>
       <c r="T13">
-        <v>1.305781550076462</v>
+        <v>1.317642559330637</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.317309842149982</v>
+        <v>7.624200688637483</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09551905208073458</v>
+        <v>0.09544602056617253</v>
       </c>
       <c r="C14">
-        <v>297.3085043699455</v>
+        <v>293.8811324983355</v>
       </c>
       <c r="D14">
-        <v>253.3085043699455</v>
+        <v>253.6811324983355</v>
       </c>
       <c r="E14">
-        <v>-176.8</v>
+        <v>-173</v>
       </c>
       <c r="F14">
-        <v>45.6</v>
+        <v>49.4</v>
       </c>
       <c r="G14">
         <v>89.59999999999999</v>
@@ -2429,45 +2429,45 @@
         <v>18.6</v>
       </c>
       <c r="M14">
-        <v>2.4396</v>
+        <v>2.68242</v>
       </c>
       <c r="N14">
-        <v>16.1604</v>
+        <v>15.91758</v>
       </c>
       <c r="O14">
-        <v>3.555288</v>
+        <v>3.5018676</v>
       </c>
       <c r="P14">
-        <v>12.605112</v>
+        <v>12.4157124</v>
       </c>
       <c r="Q14">
-        <v>45.505112</v>
+        <v>45.3157124</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1028539228190166</v>
+        <v>0.1033793109956006</v>
       </c>
       <c r="T14">
-        <v>1.317642559330637</v>
+        <v>1.329776235464217</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.624200688637483</v>
+        <v>6.934037175386405</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09544602056617253</v>
+        <v>0.09529810905161047</v>
       </c>
       <c r="C15">
-        <v>293.8811324983355</v>
+        <v>290.839188942159</v>
       </c>
       <c r="D15">
-        <v>253.6811324983355</v>
+        <v>254.4391889421589</v>
       </c>
       <c r="E15">
-        <v>-173</v>
+        <v>-169.2</v>
       </c>
       <c r="F15">
-        <v>49.4</v>
+        <v>53.2</v>
       </c>
       <c r="G15">
         <v>89.59999999999999</v>
@@ -2511,28 +2511,28 @@
         <v>18.6</v>
       </c>
       <c r="M15">
-        <v>2.68242</v>
+        <v>2.88876</v>
       </c>
       <c r="N15">
-        <v>15.91758</v>
+        <v>15.71124</v>
       </c>
       <c r="O15">
-        <v>3.5018676</v>
+        <v>3.4564728</v>
       </c>
       <c r="P15">
-        <v>12.4157124</v>
+        <v>12.2547672</v>
       </c>
       <c r="Q15">
-        <v>45.3157124</v>
+        <v>45.1547672</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1033793109956006</v>
+        <v>0.1039169175018726</v>
       </c>
       <c r="T15">
-        <v>1.329776235464217</v>
+        <v>1.342192090112532</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.934037175386405</v>
+        <v>6.438748805715948</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09529810905161047</v>
+        <v>0.09526719753704842</v>
       </c>
       <c r="C16">
-        <v>290.839188942159</v>
+        <v>287.1981852282989</v>
       </c>
       <c r="D16">
-        <v>254.4391889421589</v>
+        <v>254.5981852282989</v>
       </c>
       <c r="E16">
-        <v>-169.2</v>
+        <v>-165.4</v>
       </c>
       <c r="F16">
-        <v>53.2</v>
+        <v>57.00000000000001</v>
       </c>
       <c r="G16">
         <v>89.59999999999999</v>
@@ -2593,45 +2593,45 @@
         <v>18.6</v>
       </c>
       <c r="M16">
-        <v>2.88876</v>
+        <v>3.1521</v>
       </c>
       <c r="N16">
-        <v>15.71124</v>
+        <v>15.4479</v>
       </c>
       <c r="O16">
-        <v>3.4564728</v>
+        <v>3.398538</v>
       </c>
       <c r="P16">
-        <v>12.2547672</v>
+        <v>12.049362</v>
       </c>
       <c r="Q16">
-        <v>45.1547672</v>
+        <v>44.949362</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1039169175018726</v>
+        <v>0.1044671735729981</v>
       </c>
       <c r="T16">
-        <v>1.342192090112532</v>
+        <v>1.354900082517278</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.438748805715948</v>
+        <v>5.900828019415627</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09526719753704842</v>
+        <v>0.09512708602248635</v>
       </c>
       <c r="C17">
-        <v>287.1981852282989</v>
+        <v>284.1213606723304</v>
       </c>
       <c r="D17">
-        <v>254.5981852282989</v>
+        <v>255.3213606723304</v>
       </c>
       <c r="E17">
-        <v>-165.4</v>
+        <v>-161.6</v>
       </c>
       <c r="F17">
-        <v>57</v>
+        <v>60.8</v>
       </c>
       <c r="G17">
         <v>89.59999999999999</v>
@@ -2675,28 +2675,28 @@
         <v>18.6</v>
       </c>
       <c r="M17">
-        <v>3.1521</v>
+        <v>3.36224</v>
       </c>
       <c r="N17">
-        <v>15.4479</v>
+        <v>15.23776</v>
       </c>
       <c r="O17">
-        <v>3.398538</v>
+        <v>3.3523072</v>
       </c>
       <c r="P17">
-        <v>12.049362</v>
+        <v>11.8854528</v>
       </c>
       <c r="Q17">
-        <v>44.949362</v>
+        <v>44.7854528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1044671735729981</v>
+        <v>0.1050305309791504</v>
       </c>
       <c r="T17">
-        <v>1.354900082517278</v>
+        <v>1.367910646169756</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.900828019415628</v>
+        <v>5.532026268202151</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09512708602248635</v>
+        <v>0.0949869745079243</v>
       </c>
       <c r="C18">
-        <v>284.1213606723304</v>
+        <v>281.0486561179586</v>
       </c>
       <c r="D18">
-        <v>255.3213606723304</v>
+        <v>256.0486561179586</v>
       </c>
       <c r="E18">
-        <v>-161.6</v>
+        <v>-157.8</v>
       </c>
       <c r="F18">
-        <v>60.8</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G18">
         <v>89.59999999999999</v>
@@ -2757,28 +2757,28 @@
         <v>18.6</v>
       </c>
       <c r="M18">
-        <v>3.36224</v>
+        <v>3.572380000000001</v>
       </c>
       <c r="N18">
-        <v>15.23776</v>
+        <v>15.02762</v>
       </c>
       <c r="O18">
-        <v>3.3523072</v>
+        <v>3.3060764</v>
       </c>
       <c r="P18">
-        <v>11.8854528</v>
+        <v>11.7215436</v>
       </c>
       <c r="Q18">
-        <v>44.7854528</v>
+        <v>44.6215436</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1050305309791504</v>
+        <v>0.1056074632625594</v>
       </c>
       <c r="T18">
-        <v>1.367910646169756</v>
+        <v>1.381234717380125</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.532026268202151</v>
+        <v>5.206612958307906</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0949869745079243</v>
+        <v>0.09484686299336224</v>
       </c>
       <c r="C19">
-        <v>281.0486561179586</v>
+        <v>277.9801068738432</v>
       </c>
       <c r="D19">
-        <v>256.0486561179586</v>
+        <v>256.7801068738432</v>
       </c>
       <c r="E19">
-        <v>-157.8</v>
+        <v>-154</v>
       </c>
       <c r="F19">
-        <v>64.60000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G19">
         <v>89.59999999999999</v>
@@ -2839,28 +2839,28 @@
         <v>18.6</v>
       </c>
       <c r="M19">
-        <v>3.572380000000001</v>
+        <v>3.78252</v>
       </c>
       <c r="N19">
-        <v>15.02762</v>
+        <v>14.81748</v>
       </c>
       <c r="O19">
-        <v>3.3060764</v>
+        <v>3.2598456</v>
       </c>
       <c r="P19">
-        <v>11.7215436</v>
+        <v>11.5576344</v>
       </c>
       <c r="Q19">
-        <v>44.6215436</v>
+        <v>44.4576344</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1056074632625594</v>
+        <v>0.1061984670650759</v>
       </c>
       <c r="T19">
-        <v>1.381234717380125</v>
+        <v>1.394883765937088</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.206612958307906</v>
+        <v>4.917356682846357</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09484686299336224</v>
+        <v>0.0947067514788002</v>
       </c>
       <c r="C20">
-        <v>277.9801068738432</v>
+        <v>274.9157486532628</v>
       </c>
       <c r="D20">
-        <v>256.7801068738432</v>
+        <v>257.5157486532628</v>
       </c>
       <c r="E20">
-        <v>-154</v>
+        <v>-150.2</v>
       </c>
       <c r="F20">
-        <v>68.39999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G20">
         <v>89.59999999999999</v>
@@ -2921,28 +2921,28 @@
         <v>18.6</v>
       </c>
       <c r="M20">
-        <v>3.78252</v>
+        <v>3.99266</v>
       </c>
       <c r="N20">
-        <v>14.81748</v>
+        <v>14.60734</v>
       </c>
       <c r="O20">
-        <v>3.2598456</v>
+        <v>3.2136148</v>
       </c>
       <c r="P20">
-        <v>11.5576344</v>
+        <v>11.3937252</v>
       </c>
       <c r="Q20">
-        <v>44.4576344</v>
+        <v>44.2937252</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1061984670650759</v>
+        <v>0.1068040635540743</v>
       </c>
       <c r="T20">
-        <v>1.394883765937088</v>
+        <v>1.408869828038668</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.917356682846357</v>
+        <v>4.658548436380759</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0947067514788002</v>
+        <v>0.09495663996423816</v>
       </c>
       <c r="C21">
-        <v>274.9157486532628</v>
+        <v>269.8066636455364</v>
       </c>
       <c r="D21">
-        <v>257.5157486532628</v>
+        <v>256.2066636455365</v>
       </c>
       <c r="E21">
-        <v>-150.2</v>
+        <v>-146.4</v>
       </c>
       <c r="F21">
-        <v>72.2</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>89.59999999999999</v>
@@ -3003,45 +3003,45 @@
         <v>18.6</v>
       </c>
       <c r="M21">
-        <v>3.99266</v>
+        <v>4.3928</v>
       </c>
       <c r="N21">
-        <v>14.60734</v>
+        <v>14.2072</v>
       </c>
       <c r="O21">
-        <v>3.2136148</v>
+        <v>3.125584</v>
       </c>
       <c r="P21">
-        <v>11.3937252</v>
+        <v>11.081616</v>
       </c>
       <c r="Q21">
-        <v>44.2937252</v>
+        <v>43.981616</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1068040635540743</v>
+        <v>0.1074247999552977</v>
       </c>
       <c r="T21">
-        <v>1.408869828038668</v>
+        <v>1.423205541692787</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.658548436380759</v>
+        <v>4.234201420506283</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09495663996423816</v>
+        <v>0.09483602844967609</v>
       </c>
       <c r="C22">
-        <v>269.8066636455364</v>
+        <v>266.6368426123118</v>
       </c>
       <c r="D22">
-        <v>256.2066636455365</v>
+        <v>256.8368426123118</v>
       </c>
       <c r="E22">
-        <v>-146.4</v>
+        <v>-142.6</v>
       </c>
       <c r="F22">
-        <v>76</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="G22">
         <v>89.59999999999999</v>
@@ -3085,28 +3085,28 @@
         <v>18.6</v>
       </c>
       <c r="M22">
-        <v>4.3928</v>
+        <v>4.612440000000001</v>
       </c>
       <c r="N22">
-        <v>14.2072</v>
+        <v>13.98756</v>
       </c>
       <c r="O22">
-        <v>3.125584</v>
+        <v>3.0772632</v>
       </c>
       <c r="P22">
-        <v>11.081616</v>
+        <v>10.9102968</v>
       </c>
       <c r="Q22">
-        <v>43.981616</v>
+        <v>43.8102968</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1074247999552977</v>
+        <v>0.1080612512021216</v>
       </c>
       <c r="T22">
-        <v>1.423205541692787</v>
+        <v>1.437904184806504</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.234201420506283</v>
+        <v>4.032572781434554</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09483602844967609</v>
+        <v>0.09531601693511403</v>
       </c>
       <c r="C23">
-        <v>266.6368426123118</v>
+        <v>260.3471688719604</v>
       </c>
       <c r="D23">
-        <v>256.8368426123118</v>
+        <v>254.3471688719605</v>
       </c>
       <c r="E23">
-        <v>-142.6</v>
+        <v>-138.8</v>
       </c>
       <c r="F23">
-        <v>79.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G23">
         <v>89.59999999999999</v>
@@ -3167,45 +3167,45 @@
         <v>18.6</v>
       </c>
       <c r="M23">
-        <v>4.61244</v>
+        <v>5.12468</v>
       </c>
       <c r="N23">
-        <v>13.98756</v>
+        <v>13.47532</v>
       </c>
       <c r="O23">
-        <v>3.0772632</v>
+        <v>2.9645704</v>
       </c>
       <c r="P23">
-        <v>10.9102968</v>
+        <v>10.5107496</v>
       </c>
       <c r="Q23">
-        <v>43.8102968</v>
+        <v>43.4107496</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1080612512021216</v>
+        <v>0.1087140217116846</v>
       </c>
       <c r="T23">
-        <v>1.437904184806504</v>
+        <v>1.452979716205189</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.032572781434555</v>
+        <v>3.629494914804437</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09531601693511403</v>
+        <v>0.09572502542055199</v>
       </c>
       <c r="C24">
-        <v>260.3471688719604</v>
+        <v>254.4634413337281</v>
       </c>
       <c r="D24">
-        <v>254.3471688719605</v>
+        <v>252.2634413337281</v>
       </c>
       <c r="E24">
-        <v>-138.8</v>
+        <v>-135</v>
       </c>
       <c r="F24">
-        <v>83.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G24">
         <v>89.59999999999999</v>
@@ -3249,45 +3249,45 @@
         <v>18.6</v>
       </c>
       <c r="M24">
-        <v>5.12468</v>
+        <v>5.602340000000001</v>
       </c>
       <c r="N24">
-        <v>13.47532</v>
+        <v>12.99766</v>
       </c>
       <c r="O24">
-        <v>2.9645704</v>
+        <v>2.8594852</v>
       </c>
       <c r="P24">
-        <v>10.5107496</v>
+        <v>10.1381748</v>
       </c>
       <c r="Q24">
-        <v>43.4107496</v>
+        <v>43.0381748</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1087140217116846</v>
+        <v>0.1093837472994182</v>
       </c>
       <c r="T24">
-        <v>1.452979716205189</v>
+        <v>1.468446819847995</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.629494914804437</v>
+        <v>3.32004126846996</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09572502542055199</v>
+        <v>0.09565355390598992</v>
       </c>
       <c r="C25">
-        <v>254.4634413337281</v>
+        <v>251.0250935893478</v>
       </c>
       <c r="D25">
-        <v>252.2634413337281</v>
+        <v>252.6250935893478</v>
       </c>
       <c r="E25">
-        <v>-135</v>
+        <v>-131.2</v>
       </c>
       <c r="F25">
-        <v>87.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G25">
         <v>89.59999999999999</v>
@@ -3331,28 +3331,28 @@
         <v>18.6</v>
       </c>
       <c r="M25">
-        <v>5.602340000000001</v>
+        <v>5.84592</v>
       </c>
       <c r="N25">
-        <v>12.99766</v>
+        <v>12.75408</v>
       </c>
       <c r="O25">
-        <v>2.8594852</v>
+        <v>2.8058976</v>
       </c>
       <c r="P25">
-        <v>10.1381748</v>
+        <v>9.948182400000002</v>
       </c>
       <c r="Q25">
-        <v>43.0381748</v>
+        <v>42.8481824</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1093837472994182</v>
+        <v>0.1100710972447236</v>
       </c>
       <c r="T25">
-        <v>1.468446819847995</v>
+        <v>1.484320952534032</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.32004126846996</v>
+        <v>3.181706215617046</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09565355390598992</v>
+        <v>0.09558208239142786</v>
       </c>
       <c r="C26">
-        <v>251.0250935893478</v>
+        <v>247.5877842842297</v>
       </c>
       <c r="D26">
-        <v>252.6250935893478</v>
+        <v>252.9877842842297</v>
       </c>
       <c r="E26">
-        <v>-131.2</v>
+        <v>-127.4</v>
       </c>
       <c r="F26">
-        <v>91.2</v>
+        <v>95</v>
       </c>
       <c r="G26">
         <v>89.59999999999999</v>
@@ -3413,28 +3413,28 @@
         <v>18.6</v>
       </c>
       <c r="M26">
-        <v>5.84592</v>
+        <v>6.0895</v>
       </c>
       <c r="N26">
-        <v>12.75408</v>
+        <v>12.5105</v>
       </c>
       <c r="O26">
-        <v>2.8058976</v>
+        <v>2.75231</v>
       </c>
       <c r="P26">
-        <v>9.948182400000002</v>
+        <v>9.758190000000001</v>
       </c>
       <c r="Q26">
-        <v>42.8481824</v>
+        <v>42.65819</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1100710972447236</v>
+        <v>0.1107767765219038</v>
       </c>
       <c r="T26">
-        <v>1.484320952534032</v>
+        <v>1.500618395425031</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.181706215617046</v>
+        <v>3.054437966992364</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09558208239142786</v>
+        <v>0.09709245087686583</v>
       </c>
       <c r="C27">
-        <v>247.5877842842297</v>
+        <v>236.3382518471665</v>
       </c>
       <c r="D27">
-        <v>252.9877842842297</v>
+        <v>245.5382518471666</v>
       </c>
       <c r="E27">
-        <v>-127.4</v>
+        <v>-123.6</v>
       </c>
       <c r="F27">
-        <v>95</v>
+        <v>98.8</v>
       </c>
       <c r="G27">
         <v>89.59999999999999</v>
@@ -3495,45 +3495,45 @@
         <v>18.6</v>
       </c>
       <c r="M27">
-        <v>6.0895</v>
+        <v>7.10372</v>
       </c>
       <c r="N27">
-        <v>12.5105</v>
+        <v>11.49628</v>
       </c>
       <c r="O27">
-        <v>2.75231</v>
+        <v>2.529181600000001</v>
       </c>
       <c r="P27">
-        <v>9.758190000000001</v>
+        <v>8.967098400000001</v>
       </c>
       <c r="Q27">
-        <v>42.65819</v>
+        <v>41.8670984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107767765219038</v>
+        <v>0.1115015282119808</v>
       </c>
       <c r="T27">
-        <v>1.500618395425031</v>
+        <v>1.517356309745516</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.054437966992364</v>
+        <v>2.618346443835061</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09709245087686583</v>
+        <v>0.09708181936230374</v>
       </c>
       <c r="C28">
-        <v>236.3382518471665</v>
+        <v>232.5891557256273</v>
       </c>
       <c r="D28">
-        <v>245.5382518471666</v>
+        <v>245.5891557256273</v>
       </c>
       <c r="E28">
-        <v>-123.6</v>
+        <v>-119.8</v>
       </c>
       <c r="F28">
-        <v>98.8</v>
+        <v>102.6</v>
       </c>
       <c r="G28">
         <v>89.59999999999999</v>
@@ -3577,28 +3577,28 @@
         <v>18.6</v>
       </c>
       <c r="M28">
-        <v>7.10372</v>
+        <v>7.376940000000001</v>
       </c>
       <c r="N28">
-        <v>11.49628</v>
+        <v>11.22306</v>
       </c>
       <c r="O28">
-        <v>2.529181600000001</v>
+        <v>2.4690732</v>
       </c>
       <c r="P28">
-        <v>8.967098400000001</v>
+        <v>8.7539868</v>
       </c>
       <c r="Q28">
-        <v>41.8670984</v>
+        <v>41.6539868</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1115015282119808</v>
+        <v>0.1122461361127449</v>
       </c>
       <c r="T28">
-        <v>1.517356309745516</v>
+        <v>1.534552797061083</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.618346443835061</v>
+        <v>2.521370649618947</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09708181936230374</v>
+        <v>0.09792294784774172</v>
       </c>
       <c r="C29">
-        <v>232.5891557256273</v>
+        <v>224.8259870422498</v>
       </c>
       <c r="D29">
-        <v>245.5891557256273</v>
+        <v>241.6259870422498</v>
       </c>
       <c r="E29">
-        <v>-119.8</v>
+        <v>-116</v>
       </c>
       <c r="F29">
-        <v>102.6</v>
+        <v>106.4</v>
       </c>
       <c r="G29">
         <v>89.59999999999999</v>
@@ -3659,45 +3659,45 @@
         <v>18.6</v>
       </c>
       <c r="M29">
-        <v>7.376940000000001</v>
+        <v>8.06512</v>
       </c>
       <c r="N29">
-        <v>11.22306</v>
+        <v>10.53488</v>
       </c>
       <c r="O29">
-        <v>2.4690732</v>
+        <v>2.3176736</v>
       </c>
       <c r="P29">
-        <v>8.7539868</v>
+        <v>8.2172064</v>
       </c>
       <c r="Q29">
-        <v>41.6539868</v>
+        <v>41.1172064</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1122461361127449</v>
+        <v>0.1130114275663079</v>
       </c>
       <c r="T29">
-        <v>1.534552797061083</v>
+        <v>1.55222696457986</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.521370649618947</v>
+        <v>2.30622730969905</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09792294784774172</v>
+        <v>0.09794273633317965</v>
       </c>
       <c r="C30">
-        <v>224.8259870422498</v>
+        <v>220.9342885112126</v>
       </c>
       <c r="D30">
-        <v>241.6259870422498</v>
+        <v>241.5342885112126</v>
       </c>
       <c r="E30">
-        <v>-116</v>
+        <v>-112.2</v>
       </c>
       <c r="F30">
-        <v>106.4</v>
+        <v>110.2</v>
       </c>
       <c r="G30">
         <v>89.59999999999999</v>
@@ -3741,28 +3741,28 @@
         <v>18.6</v>
       </c>
       <c r="M30">
-        <v>8.06512</v>
+        <v>8.353160000000003</v>
       </c>
       <c r="N30">
-        <v>10.53488</v>
+        <v>10.24684</v>
       </c>
       <c r="O30">
-        <v>2.3176736</v>
+        <v>2.2543048</v>
       </c>
       <c r="P30">
-        <v>8.2172064</v>
+        <v>7.992535199999999</v>
       </c>
       <c r="Q30">
-        <v>41.1172064</v>
+        <v>40.8925352</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1130114275663079</v>
+        <v>0.1137982765256051</v>
       </c>
       <c r="T30">
-        <v>1.55222696457986</v>
+        <v>1.570398995972405</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.30622730969905</v>
+        <v>2.226702230054254</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09794273633317965</v>
+        <v>0.09796252481861759</v>
       </c>
       <c r="C31">
-        <v>220.9342885112126</v>
+        <v>217.0426595540717</v>
       </c>
       <c r="D31">
-        <v>241.5342885112126</v>
+        <v>241.4426595540717</v>
       </c>
       <c r="E31">
-        <v>-112.2</v>
+        <v>-108.4</v>
       </c>
       <c r="F31">
-        <v>110.2</v>
+        <v>114</v>
       </c>
       <c r="G31">
         <v>89.59999999999999</v>
@@ -3823,28 +3823,28 @@
         <v>18.6</v>
       </c>
       <c r="M31">
-        <v>8.353159999999999</v>
+        <v>8.641200000000001</v>
       </c>
       <c r="N31">
-        <v>10.24684</v>
+        <v>9.9588</v>
       </c>
       <c r="O31">
-        <v>2.2543048</v>
+        <v>2.190936</v>
       </c>
       <c r="P31">
-        <v>7.992535200000003</v>
+        <v>7.767863999999999</v>
       </c>
       <c r="Q31">
-        <v>40.8925352</v>
+        <v>40.66786399999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1137982765256051</v>
+        <v>0.1146076068837394</v>
       </c>
       <c r="T31">
-        <v>1.570398995972405</v>
+        <v>1.589090228261881</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.226702230054255</v>
+        <v>2.152478822385779</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09796252481861759</v>
+        <v>0.09798231330405555</v>
       </c>
       <c r="C32">
-        <v>217.0426595540717</v>
+        <v>213.1511000916759</v>
       </c>
       <c r="D32">
-        <v>241.4426595540717</v>
+        <v>241.3511000916759</v>
       </c>
       <c r="E32">
-        <v>-108.4</v>
+        <v>-104.6</v>
       </c>
       <c r="F32">
-        <v>114</v>
+        <v>117.8</v>
       </c>
       <c r="G32">
         <v>89.59999999999999</v>
@@ -3905,28 +3905,28 @@
         <v>18.6</v>
       </c>
       <c r="M32">
-        <v>8.641200000000001</v>
+        <v>8.92924</v>
       </c>
       <c r="N32">
-        <v>9.9588</v>
+        <v>9.670760000000001</v>
       </c>
       <c r="O32">
-        <v>2.190936</v>
+        <v>2.1275672</v>
       </c>
       <c r="P32">
-        <v>7.767863999999999</v>
+        <v>7.543192800000002</v>
       </c>
       <c r="Q32">
-        <v>40.66786399999999</v>
+        <v>40.4431928</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1146076068837394</v>
+        <v>0.1154403960928341</v>
       </c>
       <c r="T32">
-        <v>1.589090228261881</v>
+        <v>1.608323235400326</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.152478822385779</v>
+        <v>2.083044021663658</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09798231330405555</v>
+        <v>0.09800210178949351</v>
       </c>
       <c r="C33">
-        <v>213.1511000916759</v>
+        <v>209.2596100449942</v>
       </c>
       <c r="D33">
-        <v>241.3511000916759</v>
+        <v>241.2596100449943</v>
       </c>
       <c r="E33">
-        <v>-104.6</v>
+        <v>-100.8</v>
       </c>
       <c r="F33">
-        <v>117.8</v>
+        <v>121.6</v>
       </c>
       <c r="G33">
         <v>89.59999999999999</v>
@@ -3987,28 +3987,28 @@
         <v>18.6</v>
       </c>
       <c r="M33">
-        <v>8.92924</v>
+        <v>9.217280000000001</v>
       </c>
       <c r="N33">
-        <v>9.670760000000001</v>
+        <v>9.382720000000001</v>
       </c>
       <c r="O33">
-        <v>2.1275672</v>
+        <v>2.0641984</v>
       </c>
       <c r="P33">
-        <v>7.543192800000002</v>
+        <v>7.3185216</v>
       </c>
       <c r="Q33">
-        <v>40.4431928</v>
+        <v>40.2185216</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1154403960928341</v>
+        <v>0.1162976791021963</v>
       </c>
       <c r="T33">
-        <v>1.608323235400326</v>
+        <v>1.628121919219314</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.083044021663658</v>
+        <v>2.017948895986668</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09800210178949351</v>
+        <v>0.1016769702749314</v>
       </c>
       <c r="C34">
-        <v>209.2596100449942</v>
+        <v>189.5926556736126</v>
       </c>
       <c r="D34">
-        <v>241.2596100449943</v>
+        <v>225.3926556736126</v>
       </c>
       <c r="E34">
-        <v>-100.8</v>
+        <v>-96.99999999999997</v>
       </c>
       <c r="F34">
-        <v>121.6</v>
+        <v>125.4</v>
       </c>
       <c r="G34">
         <v>89.59999999999999</v>
@@ -4069,45 +4069,45 @@
         <v>18.6</v>
       </c>
       <c r="M34">
-        <v>9.217280000000001</v>
+        <v>11.286</v>
       </c>
       <c r="N34">
-        <v>9.382720000000001</v>
+        <v>7.314000000000002</v>
       </c>
       <c r="O34">
-        <v>2.0641984</v>
+        <v>1.609080000000001</v>
       </c>
       <c r="P34">
-        <v>7.3185216</v>
+        <v>5.704920000000001</v>
       </c>
       <c r="Q34">
-        <v>40.2185216</v>
+        <v>38.60492</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1162976791021963</v>
+        <v>0.1171805526491514</v>
       </c>
       <c r="T34">
-        <v>1.628121919219314</v>
+        <v>1.648511608525437</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.017948895986668</v>
+        <v>1.648059542796385</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1016769702749314</v>
+        <v>0.1018075187603694</v>
       </c>
       <c r="C35">
-        <v>189.5926556736126</v>
+        <v>185.2672856790423</v>
       </c>
       <c r="D35">
-        <v>225.3926556736126</v>
+        <v>224.8672856790424</v>
       </c>
       <c r="E35">
-        <v>-96.99999999999997</v>
+        <v>-93.19999999999996</v>
       </c>
       <c r="F35">
-        <v>125.4</v>
+        <v>129.2</v>
       </c>
       <c r="G35">
         <v>89.59999999999999</v>
@@ -4151,28 +4151,28 @@
         <v>18.6</v>
       </c>
       <c r="M35">
-        <v>11.286</v>
+        <v>11.628</v>
       </c>
       <c r="N35">
-        <v>7.314000000000002</v>
+        <v>6.972</v>
       </c>
       <c r="O35">
-        <v>1.609080000000001</v>
+        <v>1.53384</v>
       </c>
       <c r="P35">
-        <v>5.704920000000001</v>
+        <v>5.43816</v>
       </c>
       <c r="Q35">
-        <v>38.60492</v>
+        <v>38.33816</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1171805526491514</v>
+        <v>0.1180901799399536</v>
       </c>
       <c r="T35">
-        <v>1.648511608525437</v>
+        <v>1.669519167204471</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.648059542796385</v>
+        <v>1.599587203302373</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1018075187603694</v>
+        <v>0.1019380672458073</v>
       </c>
       <c r="C36">
-        <v>185.2672856790423</v>
+        <v>180.9443591692749</v>
       </c>
       <c r="D36">
-        <v>224.8672856790424</v>
+        <v>224.3443591692749</v>
       </c>
       <c r="E36">
-        <v>-93.19999999999996</v>
+        <v>-89.39999999999998</v>
       </c>
       <c r="F36">
-        <v>129.2</v>
+        <v>133</v>
       </c>
       <c r="G36">
         <v>89.59999999999999</v>
@@ -4233,28 +4233,28 @@
         <v>18.6</v>
       </c>
       <c r="M36">
-        <v>11.628</v>
+        <v>11.97</v>
       </c>
       <c r="N36">
-        <v>6.972</v>
+        <v>6.630000000000003</v>
       </c>
       <c r="O36">
-        <v>1.53384</v>
+        <v>1.458600000000001</v>
       </c>
       <c r="P36">
-        <v>5.43816</v>
+        <v>5.171400000000002</v>
       </c>
       <c r="Q36">
-        <v>38.33816</v>
+        <v>38.0714</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1180901799399536</v>
+        <v>0.1190277957627805</v>
       </c>
       <c r="T36">
-        <v>1.669519167204471</v>
+        <v>1.6911731123044</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.599587203302373</v>
+        <v>1.553884711779449</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1019380672458073</v>
+        <v>0.1020686157312453</v>
       </c>
       <c r="C37">
-        <v>180.9443591692749</v>
+        <v>176.6238591369658</v>
       </c>
       <c r="D37">
-        <v>224.3443591692749</v>
+        <v>223.8238591369658</v>
       </c>
       <c r="E37">
-        <v>-89.39999999999998</v>
+        <v>-85.59999999999997</v>
       </c>
       <c r="F37">
-        <v>133</v>
+        <v>136.8</v>
       </c>
       <c r="G37">
         <v>89.59999999999999</v>
@@ -4315,28 +4315,28 @@
         <v>18.6</v>
       </c>
       <c r="M37">
-        <v>11.97</v>
+        <v>12.312</v>
       </c>
       <c r="N37">
-        <v>6.630000000000003</v>
+        <v>6.288</v>
       </c>
       <c r="O37">
-        <v>1.458600000000001</v>
+        <v>1.38336</v>
       </c>
       <c r="P37">
-        <v>5.171400000000002</v>
+        <v>4.904640000000001</v>
       </c>
       <c r="Q37">
-        <v>38.0714</v>
+        <v>37.80464</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1190277957627805</v>
+        <v>0.1199947120800708</v>
       </c>
       <c r="T37">
-        <v>1.6911731123044</v>
+        <v>1.713503743188701</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.553884711779449</v>
+        <v>1.510721247563353</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1020686157312453</v>
+        <v>0.1201876473764203</v>
       </c>
       <c r="C38">
-        <v>176.6238591369658</v>
+        <v>118.3057808043339</v>
       </c>
       <c r="D38">
-        <v>223.8238591369658</v>
+        <v>169.3057808043339</v>
       </c>
       <c r="E38">
-        <v>-85.59999999999999</v>
+        <v>-81.79999999999998</v>
       </c>
       <c r="F38">
-        <v>136.8</v>
+        <v>140.6</v>
       </c>
       <c r="G38">
         <v>89.59999999999999</v>
@@ -4397,45 +4397,45 @@
         <v>18.6</v>
       </c>
       <c r="M38">
-        <v>12.312</v>
+        <v>20.64008</v>
       </c>
       <c r="N38">
-        <v>6.288000000000004</v>
+        <v>-2.04008</v>
       </c>
       <c r="O38">
-        <v>1.383360000000001</v>
+        <v>-0.4488175999999999</v>
       </c>
       <c r="P38">
-        <v>4.904640000000003</v>
+        <v>-1.5912624</v>
       </c>
       <c r="Q38">
-        <v>37.80464</v>
+        <v>31.3087376</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1199947120800707</v>
+        <v>0.1216509022683364</v>
       </c>
       <c r="T38">
-        <v>1.713503743188701</v>
+        <v>1.751752939222549</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.22</v>
+        <v>0.1982550455230794</v>
       </c>
       <c r="W38">
-        <v>0.0702</v>
+        <v>0.117696159317212</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.510721247563353</v>
+        <v>0.901159297832179</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1201876473764203</v>
+        <v>0.1211976473764203</v>
       </c>
       <c r="C39">
-        <v>118.3057808043339</v>
+        <v>112.2378209334022</v>
       </c>
       <c r="D39">
-        <v>169.3057808043339</v>
+        <v>167.0378209334022</v>
       </c>
       <c r="E39">
-        <v>-81.79999999999998</v>
+        <v>-77.99999999999997</v>
       </c>
       <c r="F39">
-        <v>140.6</v>
+        <v>144.4</v>
       </c>
       <c r="G39">
         <v>89.59999999999999</v>
@@ -4479,37 +4479,37 @@
         <v>18.6</v>
       </c>
       <c r="M39">
-        <v>20.64008</v>
+        <v>21.19792</v>
       </c>
       <c r="N39">
-        <v>-2.04008</v>
+        <v>-2.597920000000002</v>
       </c>
       <c r="O39">
-        <v>-0.4488175999999999</v>
+        <v>-0.5715424000000005</v>
       </c>
       <c r="P39">
-        <v>-1.5912624</v>
+        <v>-2.026377600000002</v>
       </c>
       <c r="Q39">
-        <v>31.3087376</v>
+        <v>30.8736224</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1216509022683364</v>
+        <v>0.1228743039178257</v>
       </c>
       <c r="T39">
-        <v>1.751752939222549</v>
+        <v>1.780007018887429</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1982550455230794</v>
+        <v>0.1930378074829983</v>
       </c>
       <c r="W39">
-        <v>0.117696159317212</v>
+        <v>0.1184620498614958</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.901159297832179</v>
+        <v>0.8774445794681741</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1211976473764203</v>
+        <v>0.1222076473764204</v>
       </c>
       <c r="C40">
-        <v>112.2378209334022</v>
+        <v>106.2298194448653</v>
       </c>
       <c r="D40">
-        <v>167.0378209334022</v>
+        <v>164.8298194448653</v>
       </c>
       <c r="E40">
-        <v>-77.99999999999997</v>
+        <v>-74.19999999999996</v>
       </c>
       <c r="F40">
-        <v>144.4</v>
+        <v>148.2</v>
       </c>
       <c r="G40">
         <v>89.59999999999999</v>
@@ -4561,37 +4561,37 @@
         <v>18.6</v>
       </c>
       <c r="M40">
-        <v>21.19792</v>
+        <v>21.75576000000001</v>
       </c>
       <c r="N40">
-        <v>-2.597920000000002</v>
+        <v>-3.155760000000004</v>
       </c>
       <c r="O40">
-        <v>-0.5715424000000005</v>
+        <v>-0.694267200000001</v>
       </c>
       <c r="P40">
-        <v>-2.026377600000002</v>
+        <v>-2.461492800000003</v>
       </c>
       <c r="Q40">
-        <v>30.8736224</v>
+        <v>30.4385072</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1228743039178257</v>
+        <v>0.1241378170968064</v>
       </c>
       <c r="T40">
-        <v>1.780007018887429</v>
+        <v>1.80918746182001</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1930378074829983</v>
+        <v>0.1880881201116394</v>
       </c>
       <c r="W40">
-        <v>0.1184620498614958</v>
+        <v>0.1191886639676114</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8774445794681741</v>
+        <v>0.8549460005074516</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1222076473764204</v>
+        <v>0.1232176473764203</v>
       </c>
       <c r="C41">
-        <v>106.2298194448653</v>
+        <v>100.2794296657771</v>
       </c>
       <c r="D41">
-        <v>164.8298194448653</v>
+        <v>162.6794296657771</v>
       </c>
       <c r="E41">
-        <v>-74.19999999999996</v>
+        <v>-70.39999999999998</v>
       </c>
       <c r="F41">
-        <v>148.2</v>
+        <v>152</v>
       </c>
       <c r="G41">
         <v>89.59999999999999</v>
@@ -4643,37 +4643,37 @@
         <v>18.6</v>
       </c>
       <c r="M41">
-        <v>21.75576000000001</v>
+        <v>22.3136</v>
       </c>
       <c r="N41">
-        <v>-3.155760000000004</v>
+        <v>-3.7136</v>
       </c>
       <c r="O41">
-        <v>-0.694267200000001</v>
+        <v>-0.8169919999999999</v>
       </c>
       <c r="P41">
-        <v>-2.461492800000003</v>
+        <v>-2.896608</v>
       </c>
       <c r="Q41">
-        <v>30.4385072</v>
+        <v>30.003392</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1241378170968064</v>
+        <v>0.1254434473817532</v>
       </c>
       <c r="T41">
-        <v>1.80918746182001</v>
+        <v>1.839340586183677</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1880881201116394</v>
+        <v>0.1833859171088484</v>
       </c>
       <c r="W41">
-        <v>0.1191886639676114</v>
+        <v>0.1198789473684211</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8549460005074516</v>
+        <v>0.8335723504947655</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1232176473764203</v>
+        <v>0.1242276473764203</v>
       </c>
       <c r="C42">
-        <v>100.2794296657771</v>
+        <v>94.38442580605604</v>
       </c>
       <c r="D42">
-        <v>162.6794296657771</v>
+        <v>160.5844258060561</v>
       </c>
       <c r="E42">
-        <v>-70.39999999999998</v>
+        <v>-66.59999999999997</v>
       </c>
       <c r="F42">
-        <v>152</v>
+        <v>155.8</v>
       </c>
       <c r="G42">
         <v>89.59999999999999</v>
@@ -4725,37 +4725,37 @@
         <v>18.6</v>
       </c>
       <c r="M42">
-        <v>22.3136</v>
+        <v>22.87144</v>
       </c>
       <c r="N42">
-        <v>-3.7136</v>
+        <v>-4.271440000000002</v>
       </c>
       <c r="O42">
-        <v>-0.8169919999999999</v>
+        <v>-0.9397168000000005</v>
       </c>
       <c r="P42">
-        <v>-2.896608</v>
+        <v>-3.331723200000002</v>
       </c>
       <c r="Q42">
-        <v>30.003392</v>
+        <v>29.5682768</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1254434473817532</v>
+        <v>0.126793336320427</v>
       </c>
       <c r="T42">
-        <v>1.839340586183677</v>
+        <v>1.870515850356282</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1833859171088484</v>
+        <v>0.1789130898622911</v>
       </c>
       <c r="W42">
-        <v>0.1198789473684211</v>
+        <v>0.1205355584082157</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8335723504947655</v>
+        <v>0.8132413175558688</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1242276473764203</v>
+        <v>0.1489349347201807</v>
       </c>
       <c r="C43">
-        <v>94.38442580605604</v>
+        <v>52.11438108175724</v>
       </c>
       <c r="D43">
-        <v>160.5844258060561</v>
+        <v>122.1143810817573</v>
       </c>
       <c r="E43">
-        <v>-66.59999999999997</v>
+        <v>-62.79999999999995</v>
       </c>
       <c r="F43">
-        <v>155.8</v>
+        <v>159.6</v>
       </c>
       <c r="G43">
         <v>89.59999999999999</v>
@@ -4807,45 +4807,45 @@
         <v>18.6</v>
       </c>
       <c r="M43">
-        <v>22.87144</v>
+        <v>32.04768000000001</v>
       </c>
       <c r="N43">
-        <v>-4.271440000000002</v>
+        <v>-13.44768000000001</v>
       </c>
       <c r="O43">
-        <v>-0.9397168000000005</v>
+        <v>-2.958489600000001</v>
       </c>
       <c r="P43">
-        <v>-3.331723200000002</v>
+        <v>-10.4891904</v>
       </c>
       <c r="Q43">
-        <v>29.5682768</v>
+        <v>22.41080959999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.126793336320427</v>
+        <v>0.1299437168496763</v>
       </c>
       <c r="T43">
-        <v>1.870515850356282</v>
+        <v>1.943272906459037</v>
       </c>
       <c r="U43">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1789130898622911</v>
+        <v>0.1276847497229128</v>
       </c>
       <c r="W43">
-        <v>0.1205355584082157</v>
+        <v>0.1751609022556391</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8132413175558688</v>
+        <v>0.5803852260132403</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1489349347201807</v>
+        <v>0.1504849347201807</v>
       </c>
       <c r="C44">
-        <v>52.11438108175727</v>
+        <v>46.50631489551324</v>
       </c>
       <c r="D44">
-        <v>122.1143810817573</v>
+        <v>120.3063148955133</v>
       </c>
       <c r="E44">
-        <v>-62.79999999999998</v>
+        <v>-58.99999999999997</v>
       </c>
       <c r="F44">
-        <v>159.6</v>
+        <v>163.4</v>
       </c>
       <c r="G44">
         <v>89.59999999999999</v>
@@ -4889,37 +4889,37 @@
         <v>18.6</v>
       </c>
       <c r="M44">
-        <v>32.04768</v>
+        <v>32.81072</v>
       </c>
       <c r="N44">
-        <v>-13.44768</v>
+        <v>-14.21072</v>
       </c>
       <c r="O44">
-        <v>-2.9584896</v>
+        <v>-3.1263584</v>
       </c>
       <c r="P44">
-        <v>-10.4891904</v>
+        <v>-11.0843616</v>
       </c>
       <c r="Q44">
-        <v>22.4108096</v>
+        <v>21.8156384</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1299437168496763</v>
+        <v>0.1314199224084425</v>
       </c>
       <c r="T44">
-        <v>1.943272906459037</v>
+        <v>1.977365413589897</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1276847497229129</v>
+        <v>0.1247153369386591</v>
       </c>
       <c r="W44">
-        <v>0.1751609022556391</v>
+        <v>0.1757571603427173</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5803852260132403</v>
+        <v>0.566887895175723</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1504849347201807</v>
+        <v>0.1520349347201806</v>
       </c>
       <c r="C45">
-        <v>46.50631489551324</v>
+        <v>40.95100918012676</v>
       </c>
       <c r="D45">
-        <v>120.3063148955133</v>
+        <v>118.5510091801268</v>
       </c>
       <c r="E45">
-        <v>-58.99999999999997</v>
+        <v>-55.19999999999999</v>
       </c>
       <c r="F45">
-        <v>163.4</v>
+        <v>167.2</v>
       </c>
       <c r="G45">
         <v>89.59999999999999</v>
@@ -4971,37 +4971,37 @@
         <v>18.6</v>
       </c>
       <c r="M45">
-        <v>32.81072</v>
+        <v>33.57376</v>
       </c>
       <c r="N45">
-        <v>-14.21072</v>
+        <v>-14.97376</v>
       </c>
       <c r="O45">
-        <v>-3.1263584</v>
+        <v>-3.2942272</v>
       </c>
       <c r="P45">
-        <v>-11.0843616</v>
+        <v>-11.6795328</v>
       </c>
       <c r="Q45">
-        <v>21.8156384</v>
+        <v>21.2204672</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1314199224084425</v>
+        <v>0.1329488495943076</v>
       </c>
       <c r="T45">
-        <v>1.977365413589897</v>
+        <v>2.012675510261145</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1247153369386591</v>
+        <v>0.1218808974627805</v>
       </c>
       <c r="W45">
-        <v>0.1757571603427173</v>
+        <v>0.1763263157894737</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.566887895175723</v>
+        <v>0.5540040793762748</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1520349347201806</v>
+        <v>0.1535849347201806</v>
       </c>
       <c r="C46">
-        <v>40.95100918012676</v>
+        <v>35.44618777158536</v>
       </c>
       <c r="D46">
-        <v>118.5510091801268</v>
+        <v>116.8461877715854</v>
       </c>
       <c r="E46">
-        <v>-55.19999999999999</v>
+        <v>-51.39999999999998</v>
       </c>
       <c r="F46">
-        <v>167.2</v>
+        <v>171</v>
       </c>
       <c r="G46">
         <v>89.59999999999999</v>
@@ -5053,37 +5053,37 @@
         <v>18.6</v>
       </c>
       <c r="M46">
-        <v>33.57376</v>
+        <v>34.3368</v>
       </c>
       <c r="N46">
-        <v>-14.97376</v>
+        <v>-15.7368</v>
       </c>
       <c r="O46">
-        <v>-3.2942272</v>
+        <v>-3.462096000000001</v>
       </c>
       <c r="P46">
-        <v>-11.6795328</v>
+        <v>-12.274704</v>
       </c>
       <c r="Q46">
-        <v>21.2204672</v>
+        <v>20.625296</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1329488495943076</v>
+        <v>0.1345333741323859</v>
       </c>
       <c r="T46">
-        <v>2.012675510261145</v>
+        <v>2.049269610447711</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1218808974627805</v>
+        <v>0.1191724330747187</v>
       </c>
       <c r="W46">
-        <v>0.1763263157894737</v>
+        <v>0.1768701754385965</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5540040793762748</v>
+        <v>0.5416928776123575</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1535849347201806</v>
+        <v>0.1551349347201807</v>
       </c>
       <c r="C47">
-        <v>35.44618777158536</v>
+        <v>29.98970357914058</v>
       </c>
       <c r="D47">
-        <v>116.8461877715854</v>
+        <v>115.1897035791406</v>
       </c>
       <c r="E47">
-        <v>-51.39999999999998</v>
+        <v>-47.59999999999997</v>
       </c>
       <c r="F47">
-        <v>171</v>
+        <v>174.8</v>
       </c>
       <c r="G47">
         <v>89.59999999999999</v>
@@ -5135,37 +5135,37 @@
         <v>18.6</v>
       </c>
       <c r="M47">
-        <v>34.3368</v>
+        <v>35.09984</v>
       </c>
       <c r="N47">
-        <v>-15.7368</v>
+        <v>-16.49984</v>
       </c>
       <c r="O47">
-        <v>-3.462096000000001</v>
+        <v>-3.6299648</v>
       </c>
       <c r="P47">
-        <v>-12.274704</v>
+        <v>-12.8698752</v>
       </c>
       <c r="Q47">
-        <v>20.625296</v>
+        <v>20.0301248</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1345333741323859</v>
+        <v>0.1361765847644671</v>
       </c>
       <c r="T47">
-        <v>2.049269610447711</v>
+        <v>2.087219047678225</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1191724330747187</v>
+        <v>0.116581728007877</v>
       </c>
       <c r="W47">
-        <v>0.1768701754385965</v>
+        <v>0.1773903890160183</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5416928776123575</v>
+        <v>0.5299169454903498</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1551349347201807</v>
+        <v>0.1566849347201807</v>
       </c>
       <c r="C48">
-        <v>29.98970357914058</v>
+        <v>24.57952956408411</v>
       </c>
       <c r="D48">
-        <v>115.1897035791406</v>
+        <v>113.5795295640841</v>
       </c>
       <c r="E48">
-        <v>-47.59999999999997</v>
+        <v>-43.79999999999995</v>
       </c>
       <c r="F48">
-        <v>174.8</v>
+        <v>178.6</v>
       </c>
       <c r="G48">
         <v>89.59999999999999</v>
@@ -5217,37 +5217,37 @@
         <v>18.6</v>
       </c>
       <c r="M48">
-        <v>35.09984</v>
+        <v>35.86288</v>
       </c>
       <c r="N48">
-        <v>-16.49984</v>
+        <v>-17.26288</v>
       </c>
       <c r="O48">
-        <v>-3.6299648</v>
+        <v>-3.797833600000001</v>
       </c>
       <c r="P48">
-        <v>-12.8698752</v>
+        <v>-13.4650464</v>
       </c>
       <c r="Q48">
-        <v>20.0301248</v>
+        <v>19.4349536</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1361765847644671</v>
+        <v>0.1378818033449288</v>
       </c>
       <c r="T48">
-        <v>2.087219047678225</v>
+        <v>2.126600539143852</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.116581728007877</v>
+        <v>0.114101265709837</v>
       </c>
       <c r="W48">
-        <v>0.1773903890160183</v>
+        <v>0.1778884658454647</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5299169454903498</v>
+        <v>0.5186421168628955</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1566849347201807</v>
+        <v>0.1582349347201807</v>
       </c>
       <c r="C49">
-        <v>24.57952956408411</v>
+        <v>19.21375046471022</v>
       </c>
       <c r="D49">
-        <v>113.5795295640841</v>
+        <v>112.0137504647102</v>
       </c>
       <c r="E49">
-        <v>-43.79999999999995</v>
+        <v>-39.99999999999997</v>
       </c>
       <c r="F49">
-        <v>178.6</v>
+        <v>182.4</v>
       </c>
       <c r="G49">
         <v>89.59999999999999</v>
@@ -5299,37 +5299,37 @@
         <v>18.6</v>
       </c>
       <c r="M49">
-        <v>35.86288</v>
+        <v>36.62592</v>
       </c>
       <c r="N49">
-        <v>-17.26288</v>
+        <v>-18.02592</v>
       </c>
       <c r="O49">
-        <v>-3.797833600000001</v>
+        <v>-3.9657024</v>
       </c>
       <c r="P49">
-        <v>-13.4650464</v>
+        <v>-14.0602176</v>
       </c>
       <c r="Q49">
-        <v>19.4349536</v>
+        <v>18.8397824</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1378818033449288</v>
+        <v>0.1396526072554082</v>
       </c>
       <c r="T49">
-        <v>2.126600539143852</v>
+        <v>2.167496703358156</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.114101265709837</v>
+        <v>0.1117241560075488</v>
       </c>
       <c r="W49">
-        <v>0.1778884658454647</v>
+        <v>0.1783657894736842</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5186421168628955</v>
+        <v>0.5078370727615853</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1582349347201807</v>
+        <v>0.1773454224508564</v>
       </c>
       <c r="C50">
-        <v>19.21375046471022</v>
+        <v>-0.859239990146051</v>
       </c>
       <c r="D50">
-        <v>112.0137504647102</v>
+        <v>95.74076000985394</v>
       </c>
       <c r="E50">
-        <v>-39.99999999999997</v>
+        <v>-36.19999999999999</v>
       </c>
       <c r="F50">
-        <v>182.4</v>
+        <v>186.2</v>
       </c>
       <c r="G50">
         <v>89.59999999999999</v>
@@ -5381,45 +5381,45 @@
         <v>18.6</v>
       </c>
       <c r="M50">
-        <v>36.62592</v>
+        <v>43.90596</v>
       </c>
       <c r="N50">
-        <v>-18.02592</v>
+        <v>-25.30596</v>
       </c>
       <c r="O50">
-        <v>-3.9657024</v>
+        <v>-5.5673112</v>
       </c>
       <c r="P50">
-        <v>-14.0602176</v>
+        <v>-19.7386488</v>
       </c>
       <c r="Q50">
-        <v>18.8397824</v>
+        <v>13.1613512</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1396526072554082</v>
+        <v>0.1422977323597804</v>
       </c>
       <c r="T50">
-        <v>2.167496703358156</v>
+        <v>2.228585042951049</v>
       </c>
       <c r="U50">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1117241560075488</v>
+        <v>0.09319919209146094</v>
       </c>
       <c r="W50">
-        <v>0.1783657894736842</v>
+        <v>0.2138236305048335</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5078370727615853</v>
+        <v>0.4236326913248224</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1773454224508564</v>
+        <v>0.1792454224508565</v>
       </c>
       <c r="C51">
-        <v>-0.859239990146051</v>
+        <v>-6.022399854889386</v>
       </c>
       <c r="D51">
-        <v>95.74076000985394</v>
+        <v>94.37760014511063</v>
       </c>
       <c r="E51">
-        <v>-36.19999999999999</v>
+        <v>-32.39999999999998</v>
       </c>
       <c r="F51">
-        <v>186.2</v>
+        <v>190</v>
       </c>
       <c r="G51">
         <v>89.59999999999999</v>
@@ -5463,37 +5463,37 @@
         <v>18.6</v>
       </c>
       <c r="M51">
-        <v>43.90596</v>
+        <v>44.802</v>
       </c>
       <c r="N51">
-        <v>-25.30596</v>
+        <v>-26.202</v>
       </c>
       <c r="O51">
-        <v>-5.5673112</v>
+        <v>-5.76444</v>
       </c>
       <c r="P51">
-        <v>-19.7386488</v>
+        <v>-20.43756</v>
       </c>
       <c r="Q51">
-        <v>13.1613512</v>
+        <v>12.46244</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1422977323597804</v>
+        <v>0.144227687006976</v>
       </c>
       <c r="T51">
-        <v>2.228585042951049</v>
+        <v>2.27315674381007</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.09319919209146094</v>
+        <v>0.09133520824963173</v>
       </c>
       <c r="W51">
-        <v>0.2138236305048335</v>
+        <v>0.2142631578947368</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4236326913248224</v>
+        <v>0.415160037498326</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1792454224508565</v>
+        <v>0.1811454224508564</v>
       </c>
       <c r="C52">
-        <v>-6.022399854889386</v>
+        <v>-11.14728722107139</v>
       </c>
       <c r="D52">
-        <v>94.37760014511063</v>
+        <v>93.05271277892862</v>
       </c>
       <c r="E52">
-        <v>-32.39999999999998</v>
+        <v>-28.59999999999997</v>
       </c>
       <c r="F52">
-        <v>190</v>
+        <v>193.8</v>
       </c>
       <c r="G52">
         <v>89.59999999999999</v>
@@ -5545,37 +5545,37 @@
         <v>18.6</v>
       </c>
       <c r="M52">
-        <v>44.802</v>
+        <v>45.69804000000001</v>
       </c>
       <c r="N52">
-        <v>-26.202</v>
+        <v>-27.09804</v>
       </c>
       <c r="O52">
-        <v>-5.76444</v>
+        <v>-5.961568800000001</v>
       </c>
       <c r="P52">
-        <v>-20.43756</v>
+        <v>-21.1364712</v>
       </c>
       <c r="Q52">
-        <v>12.46244</v>
+        <v>11.7635288</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.144227687006976</v>
+        <v>0.1462364153132408</v>
       </c>
       <c r="T52">
-        <v>2.27315674381007</v>
+        <v>2.319547697765378</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.09133520824963173</v>
+        <v>0.08954432181336441</v>
       </c>
       <c r="W52">
-        <v>0.2142631578947368</v>
+        <v>0.2146854489164087</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.415160037498326</v>
+        <v>0.4070196446062019</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1811454224508564</v>
+        <v>0.1830454224508564</v>
       </c>
       <c r="C53">
-        <v>-11.14728722107139</v>
+        <v>-16.23549160066204</v>
       </c>
       <c r="D53">
-        <v>93.05271277892862</v>
+        <v>91.76450839933796</v>
       </c>
       <c r="E53">
-        <v>-28.59999999999997</v>
+        <v>-24.79999999999998</v>
       </c>
       <c r="F53">
-        <v>193.8</v>
+        <v>197.6</v>
       </c>
       <c r="G53">
         <v>89.59999999999999</v>
@@ -5627,37 +5627,37 @@
         <v>18.6</v>
       </c>
       <c r="M53">
-        <v>45.69804000000001</v>
+        <v>46.59408</v>
       </c>
       <c r="N53">
-        <v>-27.09804</v>
+        <v>-27.99408</v>
       </c>
       <c r="O53">
-        <v>-5.961568800000001</v>
+        <v>-6.158697599999999</v>
       </c>
       <c r="P53">
-        <v>-21.1364712</v>
+        <v>-21.8353824</v>
       </c>
       <c r="Q53">
-        <v>11.7635288</v>
+        <v>11.0646176</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1462364153132408</v>
+        <v>0.1483288406322667</v>
       </c>
       <c r="T53">
-        <v>2.319547697765378</v>
+        <v>2.36787160813549</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08954432181336441</v>
+        <v>0.08782231562464589</v>
       </c>
       <c r="W53">
-        <v>0.2146854489164087</v>
+        <v>0.2150914979757085</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4070196446062019</v>
+        <v>0.3991923437483904</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1830454224508564</v>
+        <v>0.1849454224508564</v>
       </c>
       <c r="C54">
-        <v>-16.23549160066204</v>
+        <v>-21.28851568789224</v>
       </c>
       <c r="D54">
-        <v>91.76450839933796</v>
+        <v>90.51148431210777</v>
       </c>
       <c r="E54">
-        <v>-24.79999999999998</v>
+        <v>-20.99999999999997</v>
       </c>
       <c r="F54">
-        <v>197.6</v>
+        <v>201.4</v>
       </c>
       <c r="G54">
         <v>89.59999999999999</v>
@@ -5709,37 +5709,37 @@
         <v>18.6</v>
       </c>
       <c r="M54">
-        <v>46.59408</v>
+        <v>47.49012</v>
       </c>
       <c r="N54">
-        <v>-27.99408</v>
+        <v>-28.89012</v>
       </c>
       <c r="O54">
-        <v>-6.158697599999999</v>
+        <v>-6.355826400000001</v>
       </c>
       <c r="P54">
-        <v>-21.8353824</v>
+        <v>-22.5342936</v>
       </c>
       <c r="Q54">
-        <v>11.0646176</v>
+        <v>10.3657064</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1483288406322667</v>
+        <v>0.1505103053265703</v>
       </c>
       <c r="T54">
-        <v>2.36787160813549</v>
+        <v>2.418251855117096</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08782231562464589</v>
+        <v>0.08616529080153935</v>
       </c>
       <c r="W54">
-        <v>0.2150914979757085</v>
+        <v>0.215482224428997</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3991923437483904</v>
+        <v>0.3916604127342698</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1849454224508564</v>
+        <v>0.1868454224508564</v>
       </c>
       <c r="C55">
-        <v>-21.28851568789224</v>
+        <v>-26.30778120679221</v>
       </c>
       <c r="D55">
-        <v>90.51148431210777</v>
+        <v>89.29221879320782</v>
       </c>
       <c r="E55">
-        <v>-20.99999999999997</v>
+        <v>-17.19999999999996</v>
       </c>
       <c r="F55">
-        <v>201.4</v>
+        <v>205.2</v>
       </c>
       <c r="G55">
         <v>89.59999999999999</v>
@@ -5791,37 +5791,37 @@
         <v>18.6</v>
       </c>
       <c r="M55">
-        <v>47.49012</v>
+        <v>48.38616</v>
       </c>
       <c r="N55">
-        <v>-28.89012</v>
+        <v>-29.78616</v>
       </c>
       <c r="O55">
-        <v>-6.355826400000001</v>
+        <v>-6.5529552</v>
       </c>
       <c r="P55">
-        <v>-22.5342936</v>
+        <v>-23.2332048</v>
       </c>
       <c r="Q55">
-        <v>10.3657064</v>
+        <v>9.666795199999996</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1505103053265703</v>
+        <v>0.1527866163119305</v>
       </c>
       <c r="T55">
-        <v>2.418251855117096</v>
+        <v>2.470822547619641</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08616529080153935</v>
+        <v>0.08456963726817751</v>
       </c>
       <c r="W55">
-        <v>0.215482224428997</v>
+        <v>0.2158584795321638</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3916604127342698</v>
+        <v>0.3844074421280796</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1868454224508564</v>
+        <v>0.1887454224508565</v>
       </c>
       <c r="C56">
-        <v>-26.30778120679221</v>
+        <v>-31.2946342923845</v>
       </c>
       <c r="D56">
-        <v>89.29221879320782</v>
+        <v>88.10536570761553</v>
       </c>
       <c r="E56">
-        <v>-17.19999999999996</v>
+        <v>-13.39999999999995</v>
       </c>
       <c r="F56">
-        <v>205.2</v>
+        <v>209</v>
       </c>
       <c r="G56">
         <v>89.59999999999999</v>
@@ -5873,37 +5873,37 @@
         <v>18.6</v>
       </c>
       <c r="M56">
-        <v>48.38616</v>
+        <v>49.28220000000001</v>
       </c>
       <c r="N56">
-        <v>-29.78616</v>
+        <v>-30.68220000000001</v>
       </c>
       <c r="O56">
-        <v>-6.5529552</v>
+        <v>-6.750084000000002</v>
       </c>
       <c r="P56">
-        <v>-23.2332048</v>
+        <v>-23.93211600000001</v>
       </c>
       <c r="Q56">
-        <v>9.666795199999996</v>
+        <v>8.967883999999991</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1527866163119305</v>
+        <v>0.1551640966744178</v>
       </c>
       <c r="T56">
-        <v>2.470822547619641</v>
+        <v>2.525729715344522</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08456963726817751</v>
+        <v>0.08303200749966519</v>
       </c>
       <c r="W56">
-        <v>0.2158584795321638</v>
+        <v>0.216221052631579</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3844074421280796</v>
+        <v>0.377418215907569</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1887454224508565</v>
+        <v>0.1906454224508564</v>
       </c>
       <c r="C57">
-        <v>-31.2946342923845</v>
+        <v>-36.25035044835249</v>
       </c>
       <c r="D57">
-        <v>88.10536570761553</v>
+        <v>86.94964955164751</v>
       </c>
       <c r="E57">
-        <v>-13.39999999999995</v>
+        <v>-9.599999999999966</v>
       </c>
       <c r="F57">
-        <v>209</v>
+        <v>212.8</v>
       </c>
       <c r="G57">
         <v>89.59999999999999</v>
@@ -5955,37 +5955,37 @@
         <v>18.6</v>
       </c>
       <c r="M57">
-        <v>49.28220000000001</v>
+        <v>50.17824</v>
       </c>
       <c r="N57">
-        <v>-30.68220000000001</v>
+        <v>-31.57824</v>
       </c>
       <c r="O57">
-        <v>-6.750084000000002</v>
+        <v>-6.9472128</v>
       </c>
       <c r="P57">
-        <v>-23.93211600000001</v>
+        <v>-24.6310272</v>
       </c>
       <c r="Q57">
-        <v>8.967883999999991</v>
+        <v>8.268972799999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1551640966744178</v>
+        <v>0.1576496443261091</v>
       </c>
       <c r="T57">
-        <v>2.525729715344522</v>
+        <v>2.583132663420534</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08303200749966519</v>
+        <v>0.08154929308002831</v>
       </c>
       <c r="W57">
-        <v>0.216221052631579</v>
+        <v>0.2165706766917293</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.377418215907569</v>
+        <v>0.3706786049092197</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1906454224508564</v>
+        <v>0.1925454224508564</v>
       </c>
       <c r="C58">
-        <v>-36.25035044835249</v>
+        <v>-41.17613911956957</v>
       </c>
       <c r="D58">
-        <v>86.94964955164751</v>
+        <v>85.82386088043046</v>
       </c>
       <c r="E58">
-        <v>-9.599999999999966</v>
+        <v>-5.799999999999955</v>
       </c>
       <c r="F58">
-        <v>212.8</v>
+        <v>216.6</v>
       </c>
       <c r="G58">
         <v>89.59999999999999</v>
@@ -6037,37 +6037,37 @@
         <v>18.6</v>
       </c>
       <c r="M58">
-        <v>50.17824</v>
+        <v>51.07428000000001</v>
       </c>
       <c r="N58">
-        <v>-31.57824</v>
+        <v>-32.47428000000001</v>
       </c>
       <c r="O58">
-        <v>-6.9472128</v>
+        <v>-7.144341600000002</v>
       </c>
       <c r="P58">
-        <v>-24.6310272</v>
+        <v>-25.32993840000001</v>
       </c>
       <c r="Q58">
-        <v>8.268972799999997</v>
+        <v>7.570061599999992</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1576496443261091</v>
+        <v>0.160250798845321</v>
       </c>
       <c r="T58">
-        <v>2.583132663420534</v>
+        <v>2.643205516058221</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08154929308002831</v>
+        <v>0.08011860372774711</v>
       </c>
       <c r="W58">
-        <v>0.2165706766917293</v>
+        <v>0.2169080332409972</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3706786049092197</v>
+        <v>0.3641754714897596</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1925454224508564</v>
+        <v>0.1944454224508565</v>
       </c>
       <c r="C59">
-        <v>-41.17613911956957</v>
+        <v>-46.0731479139489</v>
       </c>
       <c r="D59">
-        <v>85.82386088043046</v>
+        <v>84.72685208605114</v>
       </c>
       <c r="E59">
-        <v>-5.799999999999955</v>
+        <v>-1.999999999999943</v>
       </c>
       <c r="F59">
-        <v>216.6</v>
+        <v>220.4</v>
       </c>
       <c r="G59">
         <v>89.59999999999999</v>
@@ -6119,37 +6119,37 @@
         <v>18.6</v>
       </c>
       <c r="M59">
-        <v>51.07428000000001</v>
+        <v>51.97032000000001</v>
       </c>
       <c r="N59">
-        <v>-32.47428000000001</v>
+        <v>-33.37032000000001</v>
       </c>
       <c r="O59">
-        <v>-7.144341600000002</v>
+        <v>-7.341470400000001</v>
       </c>
       <c r="P59">
-        <v>-25.32993840000001</v>
+        <v>-26.0288496</v>
       </c>
       <c r="Q59">
-        <v>7.570061599999992</v>
+        <v>6.871150399999994</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.160250798845321</v>
+        <v>0.1629758178654477</v>
       </c>
       <c r="T59">
-        <v>2.643205516058221</v>
+        <v>2.706138980726275</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08011860372774711</v>
+        <v>0.07873724849106181</v>
       </c>
       <c r="W59">
-        <v>0.2169080332409972</v>
+        <v>0.2172337568058076</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3641754714897596</v>
+        <v>0.357896584050281</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1944454224508564</v>
+        <v>0.1963454224508564</v>
       </c>
       <c r="C60">
-        <v>-46.07314791394884</v>
+        <v>-50.94246650459579</v>
       </c>
       <c r="D60">
-        <v>84.72685208605114</v>
+        <v>83.65753349540421</v>
       </c>
       <c r="E60">
-        <v>-2</v>
+        <v>1.800000000000011</v>
       </c>
       <c r="F60">
-        <v>220.4</v>
+        <v>224.2</v>
       </c>
       <c r="G60">
         <v>89.59999999999999</v>
@@ -6201,37 +6201,37 @@
         <v>18.6</v>
       </c>
       <c r="M60">
-        <v>51.97031999999999</v>
+        <v>52.86636</v>
       </c>
       <c r="N60">
-        <v>-33.37031999999999</v>
+        <v>-34.26636</v>
       </c>
       <c r="O60">
-        <v>-7.341470399999999</v>
+        <v>-7.5385992</v>
       </c>
       <c r="P60">
-        <v>-26.02884959999999</v>
+        <v>-26.7277608</v>
       </c>
       <c r="Q60">
-        <v>6.871150400000005</v>
+        <v>6.1722392</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1629758178654476</v>
+        <v>0.1658337646426536</v>
       </c>
       <c r="T60">
-        <v>2.706138980726273</v>
+        <v>2.772142370500084</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07873724849106184</v>
+        <v>0.0774027188556201</v>
       </c>
       <c r="W60">
-        <v>0.2172337568058076</v>
+        <v>0.2175484388938448</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3578965840502811</v>
+        <v>0.3518305402528187</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1963454224508564</v>
+        <v>0.1982454224508564</v>
       </c>
       <c r="C61">
-        <v>-50.94246650459579</v>
+        <v>-55.78513024015342</v>
       </c>
       <c r="D61">
-        <v>83.65753349540421</v>
+        <v>82.6148697598466</v>
       </c>
       <c r="E61">
-        <v>1.800000000000011</v>
+        <v>5.600000000000023</v>
       </c>
       <c r="F61">
-        <v>224.2</v>
+        <v>228</v>
       </c>
       <c r="G61">
         <v>89.59999999999999</v>
@@ -6283,37 +6283,37 @@
         <v>18.6</v>
       </c>
       <c r="M61">
-        <v>52.86636</v>
+        <v>53.7624</v>
       </c>
       <c r="N61">
-        <v>-34.26636</v>
+        <v>-35.1624</v>
       </c>
       <c r="O61">
-        <v>-7.5385992</v>
+        <v>-7.735728</v>
       </c>
       <c r="P61">
-        <v>-26.7277608</v>
+        <v>-27.426672</v>
       </c>
       <c r="Q61">
-        <v>6.1722392</v>
+        <v>5.473328000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1658337646426536</v>
+        <v>0.16883460875872</v>
       </c>
       <c r="T61">
-        <v>2.772142370500084</v>
+        <v>2.841445929762587</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0774027188556201</v>
+        <v>0.07611267354135977</v>
       </c>
       <c r="W61">
-        <v>0.2175484388938448</v>
+        <v>0.2178526315789474</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3518305402528187</v>
+        <v>0.3459666979152717</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1982454224508564</v>
+        <v>0.2001454224508564</v>
       </c>
       <c r="C62">
-        <v>-55.78513024015342</v>
+        <v>-60.60212348848691</v>
       </c>
       <c r="D62">
-        <v>82.6148697598466</v>
+        <v>81.59787651151306</v>
       </c>
       <c r="E62">
-        <v>5.600000000000023</v>
+        <v>9.400000000000006</v>
       </c>
       <c r="F62">
-        <v>228</v>
+        <v>231.8</v>
       </c>
       <c r="G62">
         <v>89.59999999999999</v>
@@ -6365,37 +6365,37 @@
         <v>18.6</v>
       </c>
       <c r="M62">
-        <v>53.7624</v>
+        <v>54.65844</v>
       </c>
       <c r="N62">
-        <v>-35.1624</v>
+        <v>-36.05844</v>
       </c>
       <c r="O62">
-        <v>-7.735728</v>
+        <v>-7.9328568</v>
       </c>
       <c r="P62">
-        <v>-27.426672</v>
+        <v>-28.1255832</v>
       </c>
       <c r="Q62">
-        <v>5.473328000000002</v>
+        <v>4.774416800000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.16883460875872</v>
+        <v>0.1719893423166359</v>
       </c>
       <c r="T62">
-        <v>2.841445929762587</v>
+        <v>2.914303517705218</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07611267354135977</v>
+        <v>0.0748649247947801</v>
       </c>
       <c r="W62">
-        <v>0.2178526315789474</v>
+        <v>0.2181468507333909</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3459666979152717</v>
+        <v>0.340295112703546</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2001454224508564</v>
+        <v>0.2020454224508564</v>
       </c>
       <c r="C63">
-        <v>-60.60212348848691</v>
+        <v>-65.39438273640596</v>
       </c>
       <c r="D63">
-        <v>81.59787651151306</v>
+        <v>80.60561726359406</v>
       </c>
       <c r="E63">
-        <v>9.400000000000006</v>
+        <v>13.20000000000002</v>
       </c>
       <c r="F63">
-        <v>231.8</v>
+        <v>235.6</v>
       </c>
       <c r="G63">
         <v>89.59999999999999</v>
@@ -6447,37 +6447,37 @@
         <v>18.6</v>
       </c>
       <c r="M63">
-        <v>54.65844</v>
+        <v>55.55448</v>
       </c>
       <c r="N63">
-        <v>-36.05844</v>
+        <v>-36.95448</v>
       </c>
       <c r="O63">
-        <v>-7.9328568</v>
+        <v>-8.129985599999999</v>
       </c>
       <c r="P63">
-        <v>-28.1255832</v>
+        <v>-28.8244944</v>
       </c>
       <c r="Q63">
-        <v>4.774416800000001</v>
+        <v>4.0755056</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1719893423166359</v>
+        <v>0.1753101144828632</v>
       </c>
       <c r="T63">
-        <v>2.914303517705218</v>
+        <v>2.990995715539566</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0748649247947801</v>
+        <v>0.07365742600776752</v>
       </c>
       <c r="W63">
-        <v>0.2181468507333909</v>
+        <v>0.2184315789473684</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.340295112703546</v>
+        <v>0.3348064818534887</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2020454224508564</v>
+        <v>0.2039454224508565</v>
       </c>
       <c r="C64">
-        <v>-65.39438273640596</v>
+        <v>-70.16279946594122</v>
       </c>
       <c r="D64">
-        <v>80.60561726359406</v>
+        <v>79.63720053405881</v>
       </c>
       <c r="E64">
-        <v>13.20000000000002</v>
+        <v>17.00000000000003</v>
       </c>
       <c r="F64">
-        <v>235.6</v>
+        <v>239.4</v>
       </c>
       <c r="G64">
         <v>89.59999999999999</v>
@@ -6529,37 +6529,37 @@
         <v>18.6</v>
       </c>
       <c r="M64">
-        <v>55.55448</v>
+        <v>56.45052</v>
       </c>
       <c r="N64">
-        <v>-36.95448</v>
+        <v>-37.85052</v>
       </c>
       <c r="O64">
-        <v>-8.129985599999999</v>
+        <v>-8.327114400000001</v>
       </c>
       <c r="P64">
-        <v>-28.8244944</v>
+        <v>-29.5234056</v>
       </c>
       <c r="Q64">
-        <v>4.0755056</v>
+        <v>3.376594399999995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1753101144828632</v>
+        <v>0.1788103878472649</v>
       </c>
       <c r="T64">
-        <v>2.990995715539566</v>
+        <v>3.071833437581175</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07365742600776752</v>
+        <v>0.07248826051558073</v>
       </c>
       <c r="W64">
-        <v>0.2184315789473684</v>
+        <v>0.2187072681704261</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3348064818534887</v>
+        <v>0.3294920932526396</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2039454224508565</v>
+        <v>0.2058454224508564</v>
       </c>
       <c r="C65">
-        <v>-70.16279946594122</v>
+        <v>-74.90822282574501</v>
       </c>
       <c r="D65">
-        <v>79.63720053405881</v>
+        <v>78.69177717425499</v>
       </c>
       <c r="E65">
-        <v>17.00000000000003</v>
+        <v>20.80000000000004</v>
       </c>
       <c r="F65">
-        <v>239.4</v>
+        <v>243.2</v>
       </c>
       <c r="G65">
         <v>89.59999999999999</v>
@@ -6611,37 +6611,37 @@
         <v>18.6</v>
       </c>
       <c r="M65">
-        <v>56.45052</v>
+        <v>57.34656</v>
       </c>
       <c r="N65">
-        <v>-37.85052</v>
+        <v>-38.74656</v>
       </c>
       <c r="O65">
-        <v>-8.327114400000001</v>
+        <v>-8.524243200000001</v>
       </c>
       <c r="P65">
-        <v>-29.5234056</v>
+        <v>-30.2223168</v>
       </c>
       <c r="Q65">
-        <v>3.376594399999995</v>
+        <v>2.677683199999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1788103878472649</v>
+        <v>0.1825051208430223</v>
       </c>
       <c r="T65">
-        <v>3.071833437581175</v>
+        <v>3.157162144180653</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07248826051558073</v>
+        <v>0.07135563144502478</v>
       </c>
       <c r="W65">
-        <v>0.2187072681704261</v>
+        <v>0.2189743421052632</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3294920932526396</v>
+        <v>0.3243437792955671</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2058454224508564</v>
+        <v>0.2077454224508564</v>
       </c>
       <c r="C66">
-        <v>-74.90822282574501</v>
+        <v>-79.63146211444089</v>
       </c>
       <c r="D66">
-        <v>78.69177717425499</v>
+        <v>77.76853788555911</v>
       </c>
       <c r="E66">
-        <v>20.80000000000004</v>
+        <v>24.60000000000002</v>
       </c>
       <c r="F66">
-        <v>243.2</v>
+        <v>247</v>
       </c>
       <c r="G66">
         <v>89.59999999999999</v>
@@ -6693,37 +6693,37 @@
         <v>18.6</v>
       </c>
       <c r="M66">
-        <v>57.34656</v>
+        <v>58.2426</v>
       </c>
       <c r="N66">
-        <v>-38.74656</v>
+        <v>-39.6426</v>
       </c>
       <c r="O66">
-        <v>-8.524243200000001</v>
+        <v>-8.721372000000001</v>
       </c>
       <c r="P66">
-        <v>-30.2223168</v>
+        <v>-30.921228</v>
       </c>
       <c r="Q66">
-        <v>2.677683199999997</v>
+        <v>1.978771999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1825051208430223</v>
+        <v>0.1864109814385372</v>
       </c>
       <c r="T66">
-        <v>3.157162144180653</v>
+        <v>3.247366776871528</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07135563144502478</v>
+        <v>0.07025785249971671</v>
       </c>
       <c r="W66">
-        <v>0.2189743421052632</v>
+        <v>0.2192331983805668</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3243437792955671</v>
+        <v>0.3193538749987123</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2077454224508564</v>
+        <v>0.2096454224508565</v>
       </c>
       <c r="C67">
-        <v>-79.63146211444089</v>
+        <v>-84.33328909118717</v>
       </c>
       <c r="D67">
-        <v>77.76853788555911</v>
+        <v>76.86671090881286</v>
       </c>
       <c r="E67">
-        <v>24.60000000000002</v>
+        <v>28.40000000000003</v>
       </c>
       <c r="F67">
-        <v>247</v>
+        <v>250.8</v>
       </c>
       <c r="G67">
         <v>89.59999999999999</v>
@@ -6775,37 +6775,37 @@
         <v>18.6</v>
       </c>
       <c r="M67">
-        <v>58.2426</v>
+        <v>59.13864</v>
       </c>
       <c r="N67">
-        <v>-39.6426</v>
+        <v>-40.53864</v>
       </c>
       <c r="O67">
-        <v>-8.721372000000001</v>
+        <v>-8.9185008</v>
       </c>
       <c r="P67">
-        <v>-30.921228</v>
+        <v>-31.6201392</v>
       </c>
       <c r="Q67">
-        <v>1.978771999999999</v>
+        <v>1.279860799999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1864109814385372</v>
+        <v>0.1905465985396707</v>
       </c>
       <c r="T67">
-        <v>3.247366776871528</v>
+        <v>3.342877564426574</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07025785249971671</v>
+        <v>0.06919333958305433</v>
       </c>
       <c r="W67">
-        <v>0.2192331983805668</v>
+        <v>0.2194842105263158</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3193538749987123</v>
+        <v>0.3145151799229742</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2096454224508565</v>
+        <v>0.2115454224508564</v>
       </c>
       <c r="C68">
-        <v>-84.33328909118717</v>
+        <v>-89.01444012731938</v>
       </c>
       <c r="D68">
-        <v>76.86671090881286</v>
+        <v>75.98555987268065</v>
       </c>
       <c r="E68">
-        <v>28.40000000000003</v>
+        <v>32.20000000000005</v>
       </c>
       <c r="F68">
-        <v>250.8</v>
+        <v>254.6</v>
       </c>
       <c r="G68">
         <v>89.59999999999999</v>
@@ -6857,37 +6857,37 @@
         <v>18.6</v>
       </c>
       <c r="M68">
-        <v>59.13864</v>
+        <v>60.03468000000001</v>
       </c>
       <c r="N68">
-        <v>-40.53864</v>
+        <v>-41.43468000000001</v>
       </c>
       <c r="O68">
-        <v>-8.9185008</v>
+        <v>-9.115629600000002</v>
       </c>
       <c r="P68">
-        <v>-31.6201392</v>
+        <v>-32.31905040000001</v>
       </c>
       <c r="Q68">
-        <v>1.279860799999998</v>
+        <v>0.5809495999999896</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1905465985396707</v>
+        <v>0.1949328591014788</v>
       </c>
       <c r="T68">
-        <v>3.342877564426574</v>
+        <v>3.444176884560712</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06919333958305433</v>
+        <v>0.06816060317136695</v>
       </c>
       <c r="W68">
-        <v>0.2194842105263158</v>
+        <v>0.2197277297721917</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3145151799229742</v>
+        <v>0.3098209235062134</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2115454224508564</v>
+        <v>0.2134454224508564</v>
       </c>
       <c r="C69">
-        <v>-89.01444012731938</v>
+        <v>-93.67561821168022</v>
       </c>
       <c r="D69">
-        <v>75.98555987268065</v>
+        <v>75.12438178831982</v>
       </c>
       <c r="E69">
-        <v>32.20000000000005</v>
+        <v>36.00000000000006</v>
       </c>
       <c r="F69">
-        <v>254.6</v>
+        <v>258.4</v>
       </c>
       <c r="G69">
         <v>89.59999999999999</v>
@@ -6939,37 +6939,37 @@
         <v>18.6</v>
       </c>
       <c r="M69">
-        <v>60.03468000000001</v>
+        <v>60.93072000000001</v>
       </c>
       <c r="N69">
-        <v>-41.43468000000001</v>
+        <v>-42.33072000000001</v>
       </c>
       <c r="O69">
-        <v>-9.115629600000002</v>
+        <v>-9.312758400000002</v>
       </c>
       <c r="P69">
-        <v>-32.31905040000001</v>
+        <v>-33.01796160000001</v>
       </c>
       <c r="Q69">
-        <v>0.5809495999999896</v>
+        <v>-0.1179616000000081</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1949328591014788</v>
+        <v>0.1995932609484</v>
       </c>
       <c r="T69">
-        <v>3.444176884560712</v>
+        <v>3.551807412203234</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06816060317136695</v>
+        <v>0.06715824136002331</v>
       </c>
       <c r="W69">
-        <v>0.2197277297721917</v>
+        <v>0.2199640866873065</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3098209235062134</v>
+        <v>0.3052647334546514</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2134454224508564</v>
+        <v>0.2153454224508565</v>
       </c>
       <c r="C70">
-        <v>-93.67561821168022</v>
+        <v>-98.3174948211132</v>
       </c>
       <c r="D70">
-        <v>75.12438178831982</v>
+        <v>74.28250517888686</v>
       </c>
       <c r="E70">
-        <v>36.00000000000006</v>
+        <v>39.80000000000007</v>
       </c>
       <c r="F70">
-        <v>258.4</v>
+        <v>262.2</v>
       </c>
       <c r="G70">
         <v>89.59999999999999</v>
@@ -7021,37 +7021,37 @@
         <v>18.6</v>
       </c>
       <c r="M70">
-        <v>60.93072000000001</v>
+        <v>61.82676000000001</v>
       </c>
       <c r="N70">
-        <v>-42.33072000000001</v>
+        <v>-43.22676000000001</v>
       </c>
       <c r="O70">
-        <v>-9.312758400000002</v>
+        <v>-9.509887200000003</v>
       </c>
       <c r="P70">
-        <v>-33.01796160000001</v>
+        <v>-33.71687280000001</v>
       </c>
       <c r="Q70">
-        <v>-0.1179616000000081</v>
+        <v>-0.8168728000000129</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1995932609484</v>
+        <v>0.2045543338822194</v>
       </c>
       <c r="T70">
-        <v>3.551807412203234</v>
+        <v>3.666381844854953</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06715824136002331</v>
+        <v>0.06618493351422587</v>
       </c>
       <c r="W70">
-        <v>0.2199640866873065</v>
+        <v>0.2201935926773456</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3052647334546514</v>
+        <v>0.3008406068828449</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2153454224508565</v>
+        <v>0.2172454224508565</v>
       </c>
       <c r="C71">
-        <v>-98.3174948211132</v>
+        <v>-102.940711666581</v>
       </c>
       <c r="D71">
-        <v>74.28250517888686</v>
+        <v>73.45928833341902</v>
       </c>
       <c r="E71">
-        <v>39.80000000000007</v>
+        <v>43.60000000000002</v>
       </c>
       <c r="F71">
-        <v>262.2</v>
+        <v>266</v>
       </c>
       <c r="G71">
         <v>89.59999999999999</v>
@@ -7103,37 +7103,37 @@
         <v>18.6</v>
       </c>
       <c r="M71">
-        <v>61.82676000000001</v>
+        <v>62.7228</v>
       </c>
       <c r="N71">
-        <v>-43.22676000000001</v>
+        <v>-44.1228</v>
       </c>
       <c r="O71">
-        <v>-9.509887200000003</v>
+        <v>-9.707015999999999</v>
       </c>
       <c r="P71">
-        <v>-33.71687280000001</v>
+        <v>-34.415784</v>
       </c>
       <c r="Q71">
-        <v>-0.8168728000000129</v>
+        <v>-1.515784000000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2045543338822194</v>
+        <v>0.2098461450116267</v>
       </c>
       <c r="T71">
-        <v>3.666381844854953</v>
+        <v>3.788594573016784</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06618493351422587</v>
+        <v>0.06523943446402265</v>
       </c>
       <c r="W71">
-        <v>0.2201935926773456</v>
+        <v>0.2204165413533835</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3008406068828449</v>
+        <v>0.2965428839273757</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2172454224508565</v>
+        <v>0.2191454224508564</v>
       </c>
       <c r="C72">
-        <v>-102.940711666581</v>
+        <v>-107.5458823244508</v>
       </c>
       <c r="D72">
-        <v>73.45928833341902</v>
+        <v>72.65411767554917</v>
       </c>
       <c r="E72">
-        <v>43.60000000000002</v>
+        <v>47.40000000000003</v>
       </c>
       <c r="F72">
-        <v>266</v>
+        <v>269.8</v>
       </c>
       <c r="G72">
         <v>89.59999999999999</v>
@@ -7185,37 +7185,37 @@
         <v>18.6</v>
       </c>
       <c r="M72">
-        <v>62.7228</v>
+        <v>63.61884000000001</v>
       </c>
       <c r="N72">
-        <v>-44.1228</v>
+        <v>-45.01884</v>
       </c>
       <c r="O72">
-        <v>-9.707015999999999</v>
+        <v>-9.904144800000001</v>
       </c>
       <c r="P72">
-        <v>-34.415784</v>
+        <v>-35.1146952</v>
       </c>
       <c r="Q72">
-        <v>-1.515784000000004</v>
+        <v>-2.214695200000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2098461450116267</v>
+        <v>0.2155029086327173</v>
       </c>
       <c r="T72">
-        <v>3.788594573016784</v>
+        <v>3.919235765189777</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06523943446402265</v>
+        <v>0.06432056918988149</v>
       </c>
       <c r="W72">
-        <v>0.2204165413533835</v>
+        <v>0.220633209785026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2965428839273757</v>
+        <v>0.2923662235903703</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2191454224508564</v>
+        <v>0.2210454224508564</v>
       </c>
       <c r="C73">
-        <v>-107.5458823244508</v>
+        <v>-112.1335937616626</v>
       </c>
       <c r="D73">
-        <v>72.65411767554917</v>
+        <v>71.86640623833742</v>
       </c>
       <c r="E73">
-        <v>47.40000000000003</v>
+        <v>51.19999999999999</v>
       </c>
       <c r="F73">
-        <v>269.8</v>
+        <v>273.6</v>
       </c>
       <c r="G73">
         <v>89.59999999999999</v>
@@ -7267,37 +7267,37 @@
         <v>18.6</v>
       </c>
       <c r="M73">
-        <v>63.61884000000001</v>
+        <v>64.51487999999999</v>
       </c>
       <c r="N73">
-        <v>-45.01884</v>
+        <v>-45.91487999999999</v>
       </c>
       <c r="O73">
-        <v>-9.904144800000001</v>
+        <v>-10.1012736</v>
       </c>
       <c r="P73">
-        <v>-35.1146952</v>
+        <v>-35.81360639999999</v>
       </c>
       <c r="Q73">
-        <v>-2.214695200000001</v>
+        <v>-2.913606399999992</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2155029086327173</v>
+        <v>0.2215637267981715</v>
       </c>
       <c r="T73">
-        <v>3.919235765189776</v>
+        <v>4.05920847108941</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06432056918988149</v>
+        <v>0.06342722795113316</v>
       </c>
       <c r="W73">
-        <v>0.220633209785026</v>
+        <v>0.2208438596491228</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2923662235903703</v>
+        <v>0.2883055815960598</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2210454224508564</v>
+        <v>0.2229454224508564</v>
       </c>
       <c r="C74">
-        <v>-112.1335937616626</v>
+        <v>-116.7044077627453</v>
       </c>
       <c r="D74">
-        <v>71.86640623833742</v>
+        <v>71.09559223725462</v>
       </c>
       <c r="E74">
-        <v>51.19999999999999</v>
+        <v>55</v>
       </c>
       <c r="F74">
-        <v>273.6</v>
+        <v>277.4</v>
       </c>
       <c r="G74">
         <v>89.59999999999999</v>
@@ -7349,37 +7349,37 @@
         <v>18.6</v>
       </c>
       <c r="M74">
-        <v>64.51487999999999</v>
+        <v>65.41092</v>
       </c>
       <c r="N74">
-        <v>-45.91487999999999</v>
+        <v>-46.81092</v>
       </c>
       <c r="O74">
-        <v>-10.1012736</v>
+        <v>-10.2984024</v>
       </c>
       <c r="P74">
-        <v>-35.81360639999999</v>
+        <v>-36.5125176</v>
       </c>
       <c r="Q74">
-        <v>-2.913606399999992</v>
+        <v>-3.612517600000004</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2215637267981715</v>
+        <v>0.228073494457363</v>
       </c>
       <c r="T74">
-        <v>4.05920847108941</v>
+        <v>4.209549525574203</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06342722795113316</v>
+        <v>0.06255836181481625</v>
       </c>
       <c r="W74">
-        <v>0.2208438596491228</v>
+        <v>0.2210487382840663</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2883055815960598</v>
+        <v>0.2843561900673466</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2229454224508564</v>
+        <v>0.2248454224508564</v>
       </c>
       <c r="C75">
-        <v>-116.7044077627453</v>
+        <v>-121.2588622659754</v>
       </c>
       <c r="D75">
-        <v>71.09559223725462</v>
+        <v>70.34113773402457</v>
       </c>
       <c r="E75">
-        <v>55</v>
+        <v>58.80000000000001</v>
       </c>
       <c r="F75">
-        <v>277.4</v>
+        <v>281.2</v>
       </c>
       <c r="G75">
         <v>89.59999999999999</v>
@@ -7431,37 +7431,37 @@
         <v>18.6</v>
       </c>
       <c r="M75">
-        <v>65.41092</v>
+        <v>66.30696</v>
       </c>
       <c r="N75">
-        <v>-46.81092</v>
+        <v>-47.70696</v>
       </c>
       <c r="O75">
-        <v>-10.2984024</v>
+        <v>-10.4955312</v>
       </c>
       <c r="P75">
-        <v>-36.5125176</v>
+        <v>-37.2114288</v>
       </c>
       <c r="Q75">
-        <v>-3.612517600000004</v>
+        <v>-4.311428800000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.228073494457363</v>
+        <v>0.2350840134749539</v>
       </c>
       <c r="T75">
-        <v>4.209549525574203</v>
+        <v>4.371455276557827</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06255836181481625</v>
+        <v>0.06171297854704845</v>
       </c>
       <c r="W75">
-        <v>0.2210487382840663</v>
+        <v>0.221248079658606</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2843561900673466</v>
+        <v>0.2805135388502202</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2248454224508564</v>
+        <v>0.2267454224508564</v>
       </c>
       <c r="C76">
-        <v>-121.2588622659754</v>
+        <v>-125.7974726153527</v>
       </c>
       <c r="D76">
-        <v>70.34113773402457</v>
+        <v>69.60252738464729</v>
       </c>
       <c r="E76">
-        <v>58.80000000000001</v>
+        <v>62.60000000000002</v>
       </c>
       <c r="F76">
-        <v>281.2</v>
+        <v>285</v>
       </c>
       <c r="G76">
         <v>89.59999999999999</v>
@@ -7513,37 +7513,37 @@
         <v>18.6</v>
       </c>
       <c r="M76">
-        <v>66.30696</v>
+        <v>67.203</v>
       </c>
       <c r="N76">
-        <v>-47.70696</v>
+        <v>-48.603</v>
       </c>
       <c r="O76">
-        <v>-10.4955312</v>
+        <v>-10.69266</v>
       </c>
       <c r="P76">
-        <v>-37.2114288</v>
+        <v>-37.91034000000001</v>
       </c>
       <c r="Q76">
-        <v>-4.311428800000002</v>
+        <v>-5.010340000000006</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2350840134749539</v>
+        <v>0.242655374013952</v>
       </c>
       <c r="T76">
-        <v>4.371455276557827</v>
+        <v>4.546313487620139</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06171297854704845</v>
+        <v>0.06089013883308781</v>
       </c>
       <c r="W76">
-        <v>0.221248079658606</v>
+        <v>0.2214421052631579</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2805135388502202</v>
+        <v>0.2767733583322173</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2267454224508564</v>
+        <v>0.2286454224508564</v>
       </c>
       <c r="C77">
-        <v>-125.7974726153527</v>
+        <v>-130.3207327345191</v>
       </c>
       <c r="D77">
-        <v>69.60252738464729</v>
+        <v>68.87926726548088</v>
       </c>
       <c r="E77">
-        <v>62.60000000000002</v>
+        <v>66.40000000000003</v>
       </c>
       <c r="F77">
-        <v>285</v>
+        <v>288.8</v>
       </c>
       <c r="G77">
         <v>89.59999999999999</v>
@@ -7595,37 +7595,37 @@
         <v>18.6</v>
       </c>
       <c r="M77">
-        <v>67.203</v>
+        <v>68.09904</v>
       </c>
       <c r="N77">
-        <v>-48.603</v>
+        <v>-49.49904</v>
       </c>
       <c r="O77">
-        <v>-10.69266</v>
+        <v>-10.8897888</v>
       </c>
       <c r="P77">
-        <v>-37.91034000000001</v>
+        <v>-38.6092512</v>
       </c>
       <c r="Q77">
-        <v>-5.010340000000006</v>
+        <v>-5.709251200000004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.242655374013952</v>
+        <v>0.2508576812645334</v>
       </c>
       <c r="T77">
-        <v>4.546313487620139</v>
+        <v>4.735743216270979</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06089013883308781</v>
+        <v>0.06008895279581034</v>
       </c>
       <c r="W77">
-        <v>0.2214421052631579</v>
+        <v>0.2216310249307479</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2767733583322173</v>
+        <v>0.2731316036173197</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2286454224508564</v>
+        <v>0.2305454224508565</v>
       </c>
       <c r="C78">
-        <v>-130.3207327345191</v>
+        <v>-134.8291162282385</v>
       </c>
       <c r="D78">
-        <v>68.87926726548088</v>
+        <v>68.17088377176147</v>
       </c>
       <c r="E78">
-        <v>66.40000000000003</v>
+        <v>70.20000000000005</v>
       </c>
       <c r="F78">
-        <v>288.8</v>
+        <v>292.6</v>
       </c>
       <c r="G78">
         <v>89.59999999999999</v>
@@ -7677,37 +7677,37 @@
         <v>18.6</v>
       </c>
       <c r="M78">
-        <v>68.09904</v>
+        <v>68.99508</v>
       </c>
       <c r="N78">
-        <v>-49.49904</v>
+        <v>-50.39508</v>
       </c>
       <c r="O78">
-        <v>-10.8897888</v>
+        <v>-11.0869176</v>
       </c>
       <c r="P78">
-        <v>-38.6092512</v>
+        <v>-39.3081624</v>
       </c>
       <c r="Q78">
-        <v>-5.709251200000004</v>
+        <v>-6.408162400000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2508576812645334</v>
+        <v>0.2597732326238609</v>
       </c>
       <c r="T78">
-        <v>4.735743216270979</v>
+        <v>4.941645095239283</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06008895279581034</v>
+        <v>0.05930857678547514</v>
       </c>
       <c r="W78">
-        <v>0.2216310249307479</v>
+        <v>0.221815037593985</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2731316036173197</v>
+        <v>0.269584439933978</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2305454224508565</v>
+        <v>0.2324454224508564</v>
       </c>
       <c r="C79">
-        <v>-134.8291162282385</v>
+        <v>-139.3230774166008</v>
       </c>
       <c r="D79">
-        <v>68.17088377176147</v>
+        <v>67.47692258339929</v>
       </c>
       <c r="E79">
-        <v>70.20000000000005</v>
+        <v>74.00000000000006</v>
       </c>
       <c r="F79">
-        <v>292.6</v>
+        <v>296.4</v>
       </c>
       <c r="G79">
         <v>89.59999999999999</v>
@@ -7759,37 +7759,37 @@
         <v>18.6</v>
       </c>
       <c r="M79">
-        <v>68.99508</v>
+        <v>69.89112000000002</v>
       </c>
       <c r="N79">
-        <v>-50.39508</v>
+        <v>-51.29112000000001</v>
       </c>
       <c r="O79">
-        <v>-11.0869176</v>
+        <v>-11.2840464</v>
       </c>
       <c r="P79">
-        <v>-39.3081624</v>
+        <v>-40.00707360000001</v>
       </c>
       <c r="Q79">
-        <v>-6.408162400000002</v>
+        <v>-7.107073600000014</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2597732326238609</v>
+        <v>0.2694992886522182</v>
       </c>
       <c r="T79">
-        <v>4.941645095239283</v>
+        <v>5.166265326841068</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05930857678547514</v>
+        <v>0.05854821041643058</v>
       </c>
       <c r="W79">
-        <v>0.221815037593985</v>
+        <v>0.2219943319838057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.269584439933978</v>
+        <v>0.2661282291655935</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2324454224508564</v>
+        <v>0.2343454224508565</v>
       </c>
       <c r="C80">
-        <v>-139.3230774166008</v>
+        <v>-143.8030523066932</v>
       </c>
       <c r="D80">
-        <v>67.47692258339929</v>
+        <v>66.79694769330682</v>
       </c>
       <c r="E80">
-        <v>74.00000000000006</v>
+        <v>77.80000000000001</v>
       </c>
       <c r="F80">
-        <v>296.4</v>
+        <v>300.2</v>
       </c>
       <c r="G80">
         <v>89.59999999999999</v>
@@ -7841,37 +7841,37 @@
         <v>18.6</v>
       </c>
       <c r="M80">
-        <v>69.89112000000002</v>
+        <v>70.78716</v>
       </c>
       <c r="N80">
-        <v>-51.29112000000001</v>
+        <v>-52.18716</v>
       </c>
       <c r="O80">
-        <v>-11.2840464</v>
+        <v>-11.4811752</v>
       </c>
       <c r="P80">
-        <v>-40.00707360000001</v>
+        <v>-40.7059848</v>
       </c>
       <c r="Q80">
-        <v>-7.107073600000014</v>
+        <v>-7.805984799999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2694992886522182</v>
+        <v>0.2801516357308954</v>
       </c>
       <c r="T80">
-        <v>5.166265326841068</v>
+        <v>5.412277961452549</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05854821041643058</v>
+        <v>0.05780709382888083</v>
       </c>
       <c r="W80">
-        <v>0.2219943319838057</v>
+        <v>0.2221690872751499</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2661282291655935</v>
+        <v>0.2627595174040038</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2343454224508565</v>
+        <v>0.2362454224508564</v>
       </c>
       <c r="C81">
-        <v>-143.8030523066932</v>
+        <v>-148.2694595061103</v>
       </c>
       <c r="D81">
-        <v>66.79694769330682</v>
+        <v>66.13054049388977</v>
       </c>
       <c r="E81">
-        <v>77.80000000000001</v>
+        <v>81.60000000000002</v>
       </c>
       <c r="F81">
-        <v>300.2</v>
+        <v>304</v>
       </c>
       <c r="G81">
         <v>89.59999999999999</v>
@@ -7923,37 +7923,37 @@
         <v>18.6</v>
       </c>
       <c r="M81">
-        <v>70.78716</v>
+        <v>71.6832</v>
       </c>
       <c r="N81">
-        <v>-52.18716</v>
+        <v>-53.0832</v>
       </c>
       <c r="O81">
-        <v>-11.4811752</v>
+        <v>-11.678304</v>
       </c>
       <c r="P81">
-        <v>-40.7059848</v>
+        <v>-41.404896</v>
       </c>
       <c r="Q81">
-        <v>-7.805984799999997</v>
+        <v>-8.504896000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2801516357308954</v>
+        <v>0.2918692175174401</v>
       </c>
       <c r="T81">
-        <v>5.412277961452549</v>
+        <v>5.682891859525176</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05780709382888083</v>
+        <v>0.05708450515601982</v>
       </c>
       <c r="W81">
-        <v>0.2221690872751499</v>
+        <v>0.2223394736842105</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2627595174040038</v>
+        <v>0.2594750234364538</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2362454224508564</v>
+        <v>0.2381454224508564</v>
       </c>
       <c r="C82">
-        <v>-148.2694595061103</v>
+        <v>-152.7227010823193</v>
       </c>
       <c r="D82">
-        <v>66.13054049388977</v>
+        <v>65.47729891768068</v>
       </c>
       <c r="E82">
-        <v>81.60000000000002</v>
+        <v>85.40000000000003</v>
       </c>
       <c r="F82">
-        <v>304</v>
+        <v>307.8</v>
       </c>
       <c r="G82">
         <v>89.59999999999999</v>
@@ -8005,37 +8005,37 @@
         <v>18.6</v>
       </c>
       <c r="M82">
-        <v>71.6832</v>
+        <v>72.57924</v>
       </c>
       <c r="N82">
-        <v>-53.0832</v>
+        <v>-53.97924</v>
       </c>
       <c r="O82">
-        <v>-11.678304</v>
+        <v>-11.8754328</v>
       </c>
       <c r="P82">
-        <v>-41.404896</v>
+        <v>-42.1038072</v>
       </c>
       <c r="Q82">
-        <v>-8.504896000000002</v>
+        <v>-9.2038072</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2918692175174401</v>
+        <v>0.3048202289657264</v>
       </c>
       <c r="T82">
-        <v>5.682891859525176</v>
+        <v>5.981991431079132</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05708450515601982</v>
+        <v>0.05637975817878502</v>
       </c>
       <c r="W82">
-        <v>0.2223394736842105</v>
+        <v>0.2225056530214425</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2594750234364538</v>
+        <v>0.2562716280853864</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2381454224508564</v>
+        <v>0.2400454224508565</v>
       </c>
       <c r="C83">
-        <v>-152.7227010823193</v>
+        <v>-157.1631633715919</v>
       </c>
       <c r="D83">
-        <v>65.47729891768068</v>
+        <v>64.83683662840815</v>
       </c>
       <c r="E83">
-        <v>85.40000000000003</v>
+        <v>89.20000000000005</v>
       </c>
       <c r="F83">
-        <v>307.8</v>
+        <v>311.6</v>
       </c>
       <c r="G83">
         <v>89.59999999999999</v>
@@ -8087,37 +8087,37 @@
         <v>18.6</v>
       </c>
       <c r="M83">
-        <v>72.57924</v>
+        <v>73.47528000000001</v>
       </c>
       <c r="N83">
-        <v>-53.97924</v>
+        <v>-54.87528000000001</v>
       </c>
       <c r="O83">
-        <v>-11.8754328</v>
+        <v>-12.0725616</v>
       </c>
       <c r="P83">
-        <v>-42.1038072</v>
+        <v>-42.80271840000001</v>
       </c>
       <c r="Q83">
-        <v>-9.2038072</v>
+        <v>-9.902718400000012</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3048202289657264</v>
+        <v>0.3192102416860446</v>
       </c>
       <c r="T83">
-        <v>5.981991431079132</v>
+        <v>6.314324288361306</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05637975817878502</v>
+        <v>0.05569220015221445</v>
       </c>
       <c r="W83">
-        <v>0.2225056530214425</v>
+        <v>0.2226677792041079</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2562716280853864</v>
+        <v>0.2531463643282476</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2400454224508565</v>
+        <v>0.2419454224508565</v>
       </c>
       <c r="C84">
-        <v>-157.1631633715919</v>
+        <v>-161.5912177409201</v>
       </c>
       <c r="D84">
-        <v>64.83683662840815</v>
+        <v>64.20878225908</v>
       </c>
       <c r="E84">
-        <v>89.20000000000005</v>
+        <v>93.00000000000006</v>
       </c>
       <c r="F84">
-        <v>311.6</v>
+        <v>315.4</v>
       </c>
       <c r="G84">
         <v>89.59999999999999</v>
@@ -8169,37 +8169,37 @@
         <v>18.6</v>
       </c>
       <c r="M84">
-        <v>73.47528000000001</v>
+        <v>74.37132000000001</v>
       </c>
       <c r="N84">
-        <v>-54.87528000000001</v>
+        <v>-55.77132000000001</v>
       </c>
       <c r="O84">
-        <v>-12.0725616</v>
+        <v>-12.2696904</v>
       </c>
       <c r="P84">
-        <v>-42.80271840000001</v>
+        <v>-43.50162960000001</v>
       </c>
       <c r="Q84">
-        <v>-9.902718400000012</v>
+        <v>-10.60162960000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3192102416860446</v>
+        <v>0.3352931970793414</v>
       </c>
       <c r="T84">
-        <v>6.314324288361306</v>
+        <v>6.685755128853149</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05569220015221445</v>
+        <v>0.05502120978893477</v>
       </c>
       <c r="W84">
-        <v>0.2226677792041079</v>
+        <v>0.2228259987317692</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2531463643282476</v>
+        <v>0.2500964081315217</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2419454224508565</v>
+        <v>0.2438454224508564</v>
       </c>
       <c r="C85">
-        <v>-161.5912177409201</v>
+        <v>-166.0072213060745</v>
       </c>
       <c r="D85">
-        <v>64.20878225908</v>
+        <v>63.59277869392552</v>
       </c>
       <c r="E85">
-        <v>93.00000000000006</v>
+        <v>96.80000000000007</v>
       </c>
       <c r="F85">
-        <v>315.4</v>
+        <v>319.2</v>
       </c>
       <c r="G85">
         <v>89.59999999999999</v>
@@ -8251,37 +8251,37 @@
         <v>18.6</v>
       </c>
       <c r="M85">
-        <v>74.37132000000001</v>
+        <v>75.26736000000001</v>
       </c>
       <c r="N85">
-        <v>-55.77132000000001</v>
+        <v>-56.66736000000001</v>
       </c>
       <c r="O85">
-        <v>-12.2696904</v>
+        <v>-12.4668192</v>
       </c>
       <c r="P85">
-        <v>-43.50162960000001</v>
+        <v>-44.20054080000001</v>
       </c>
       <c r="Q85">
-        <v>-10.60162960000001</v>
+        <v>-11.30054080000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3352931970793414</v>
+        <v>0.3533865218968003</v>
       </c>
       <c r="T85">
-        <v>6.685755128853149</v>
+        <v>7.103614824406472</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05502120978893477</v>
+        <v>0.05436619538668554</v>
       </c>
       <c r="W85">
-        <v>0.2228259987317692</v>
+        <v>0.2229804511278196</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2500964081315217</v>
+        <v>0.2471190699394797</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2438454224508564</v>
+        <v>0.2457454224508564</v>
       </c>
       <c r="C86">
-        <v>-166.0072213060745</v>
+        <v>-170.4115176087225</v>
       </c>
       <c r="D86">
-        <v>63.59277869392552</v>
+        <v>62.98848239127748</v>
       </c>
       <c r="E86">
-        <v>96.80000000000001</v>
+        <v>100.6</v>
       </c>
       <c r="F86">
-        <v>319.2</v>
+        <v>323</v>
       </c>
       <c r="G86">
         <v>89.59999999999999</v>
@@ -8333,37 +8333,37 @@
         <v>18.6</v>
       </c>
       <c r="M86">
-        <v>75.26736</v>
+        <v>76.16340000000001</v>
       </c>
       <c r="N86">
-        <v>-56.66736</v>
+        <v>-57.56340000000001</v>
       </c>
       <c r="O86">
-        <v>-12.4668192</v>
+        <v>-12.663948</v>
       </c>
       <c r="P86">
-        <v>-44.2005408</v>
+        <v>-44.89945200000001</v>
       </c>
       <c r="Q86">
-        <v>-11.3005408</v>
+        <v>-11.99945200000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3533865218968</v>
+        <v>0.3738922900232534</v>
       </c>
       <c r="T86">
-        <v>7.103614824406467</v>
+        <v>7.577189146033565</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05436619538668555</v>
+        <v>0.05372659308801866</v>
       </c>
       <c r="W86">
-        <v>0.2229804511278196</v>
+        <v>0.2231312693498452</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2471190699394797</v>
+        <v>0.2442117867637211</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2457454224508564</v>
+        <v>0.2476454224508564</v>
       </c>
       <c r="C87">
-        <v>-170.4115176087225</v>
+        <v>-174.8044372553029</v>
       </c>
       <c r="D87">
-        <v>62.98848239127748</v>
+        <v>62.3955627446971</v>
       </c>
       <c r="E87">
-        <v>100.6</v>
+        <v>104.4</v>
       </c>
       <c r="F87">
-        <v>323</v>
+        <v>326.8</v>
       </c>
       <c r="G87">
         <v>89.59999999999999</v>
@@ -8415,37 +8415,37 @@
         <v>18.6</v>
       </c>
       <c r="M87">
-        <v>76.16340000000001</v>
+        <v>77.05944000000001</v>
       </c>
       <c r="N87">
-        <v>-57.56340000000001</v>
+        <v>-58.45944000000001</v>
       </c>
       <c r="O87">
-        <v>-12.663948</v>
+        <v>-12.8610768</v>
       </c>
       <c r="P87">
-        <v>-44.89945200000001</v>
+        <v>-45.59836320000001</v>
       </c>
       <c r="Q87">
-        <v>-11.99945200000001</v>
+        <v>-12.69836320000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3738922900232534</v>
+        <v>0.3973274535963429</v>
       </c>
       <c r="T87">
-        <v>7.577189146033565</v>
+        <v>8.11841694217882</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05372659308801866</v>
+        <v>0.05310186526141378</v>
       </c>
       <c r="W87">
-        <v>0.2231312693498452</v>
+        <v>0.2232785801713586</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2442117867637211</v>
+        <v>0.2413721148246081</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2476454224508564</v>
+        <v>0.2495454224508564</v>
       </c>
       <c r="C88">
-        <v>-174.8044372553029</v>
+        <v>-179.1862985201543</v>
       </c>
       <c r="D88">
-        <v>62.3955627446971</v>
+        <v>61.81370147984578</v>
       </c>
       <c r="E88">
-        <v>104.4</v>
+        <v>108.2</v>
       </c>
       <c r="F88">
-        <v>326.8</v>
+        <v>330.6</v>
       </c>
       <c r="G88">
         <v>89.59999999999999</v>
@@ -8497,37 +8497,37 @@
         <v>18.6</v>
       </c>
       <c r="M88">
-        <v>77.05944000000001</v>
+        <v>77.95548000000001</v>
       </c>
       <c r="N88">
-        <v>-58.45944000000001</v>
+        <v>-59.35548000000001</v>
       </c>
       <c r="O88">
-        <v>-12.8610768</v>
+        <v>-13.0582056</v>
       </c>
       <c r="P88">
-        <v>-45.59836320000001</v>
+        <v>-46.29727440000001</v>
       </c>
       <c r="Q88">
-        <v>-12.69836320000001</v>
+        <v>-13.39727440000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3973274535963429</v>
+        <v>0.4243680269499077</v>
       </c>
       <c r="T88">
-        <v>8.11841694217882</v>
+        <v>8.742910553115651</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05310186526141378</v>
+        <v>0.05249149899404121</v>
       </c>
       <c r="W88">
-        <v>0.2232785801713586</v>
+        <v>0.2234225045372051</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2413721148246081</v>
+        <v>0.2385977227001873</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2495454224508564</v>
+        <v>0.2514454224508564</v>
       </c>
       <c r="C89">
-        <v>-179.1862985201543</v>
+        <v>-183.557407915209</v>
       </c>
       <c r="D89">
-        <v>61.81370147984578</v>
+        <v>61.24259208479094</v>
       </c>
       <c r="E89">
-        <v>108.2</v>
+        <v>112</v>
       </c>
       <c r="F89">
-        <v>330.6</v>
+        <v>334.4</v>
       </c>
       <c r="G89">
         <v>89.59999999999999</v>
@@ -8579,37 +8579,37 @@
         <v>18.6</v>
       </c>
       <c r="M89">
-        <v>77.95548000000001</v>
+        <v>78.85151999999999</v>
       </c>
       <c r="N89">
-        <v>-59.35548000000001</v>
+        <v>-60.25151999999999</v>
       </c>
       <c r="O89">
-        <v>-13.0582056</v>
+        <v>-13.2553344</v>
       </c>
       <c r="P89">
-        <v>-46.29727440000001</v>
+        <v>-46.99618559999999</v>
       </c>
       <c r="Q89">
-        <v>-13.39727440000001</v>
+        <v>-14.09618559999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4243680269499077</v>
+        <v>0.4559153625290667</v>
       </c>
       <c r="T89">
-        <v>8.742910553115651</v>
+        <v>9.471486432541957</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05249149899404121</v>
+        <v>0.05189500468729075</v>
       </c>
       <c r="W89">
-        <v>0.2234225045372051</v>
+        <v>0.2235631578947368</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2385977227001873</v>
+        <v>0.2358863849422307</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2514454224508564</v>
+        <v>0.2533454224508565</v>
       </c>
       <c r="C90">
-        <v>-183.557407915209</v>
+        <v>-187.9180607283958</v>
       </c>
       <c r="D90">
-        <v>61.24259208479094</v>
+        <v>60.68193927160419</v>
       </c>
       <c r="E90">
-        <v>112</v>
+        <v>115.8</v>
       </c>
       <c r="F90">
-        <v>334.4</v>
+        <v>338.2</v>
       </c>
       <c r="G90">
         <v>89.59999999999999</v>
@@ -8661,37 +8661,37 @@
         <v>18.6</v>
       </c>
       <c r="M90">
-        <v>78.85151999999999</v>
+        <v>79.74756000000001</v>
       </c>
       <c r="N90">
-        <v>-60.25151999999999</v>
+        <v>-61.14756000000001</v>
       </c>
       <c r="O90">
-        <v>-13.2553344</v>
+        <v>-13.4524632</v>
       </c>
       <c r="P90">
-        <v>-46.99618559999999</v>
+        <v>-47.6950968</v>
       </c>
       <c r="Q90">
-        <v>-14.09618559999999</v>
+        <v>-14.7950968</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4559153625290667</v>
+        <v>0.4931985773044365</v>
       </c>
       <c r="T90">
-        <v>9.471486432541957</v>
+        <v>10.33253065368214</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05189500468729075</v>
+        <v>0.05131191474698411</v>
       </c>
       <c r="W90">
-        <v>0.2235631578947368</v>
+        <v>0.2237006505026611</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2358863849422307</v>
+        <v>0.233235976122655</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2533454224508565</v>
+        <v>0.2552454224508565</v>
       </c>
       <c r="C91">
-        <v>-187.9180607283958</v>
+        <v>-192.2685415327357</v>
       </c>
       <c r="D91">
-        <v>60.68193927160419</v>
+        <v>60.13145846726431</v>
       </c>
       <c r="E91">
-        <v>115.8</v>
+        <v>119.6</v>
       </c>
       <c r="F91">
-        <v>338.2</v>
+        <v>342</v>
       </c>
       <c r="G91">
         <v>89.59999999999999</v>
@@ -8743,37 +8743,37 @@
         <v>18.6</v>
       </c>
       <c r="M91">
-        <v>79.74756000000001</v>
+        <v>80.64360000000001</v>
       </c>
       <c r="N91">
-        <v>-61.14756000000001</v>
+        <v>-62.0436</v>
       </c>
       <c r="O91">
-        <v>-13.4524632</v>
+        <v>-13.649592</v>
       </c>
       <c r="P91">
-        <v>-47.6950968</v>
+        <v>-48.394008</v>
       </c>
       <c r="Q91">
-        <v>-14.7950968</v>
+        <v>-15.494008</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4931985773044365</v>
+        <v>0.5379384350348803</v>
       </c>
       <c r="T91">
-        <v>10.33253065368214</v>
+        <v>11.36578371905035</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05131191474698411</v>
+        <v>0.05074178236090651</v>
       </c>
       <c r="W91">
-        <v>0.2237006505026611</v>
+        <v>0.2238350877192982</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.233235976122655</v>
+        <v>0.2306444652768478</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2552454224508565</v>
+        <v>0.2571454224508565</v>
       </c>
       <c r="C92">
-        <v>-192.2685415327357</v>
+        <v>-196.609124667979</v>
       </c>
       <c r="D92">
-        <v>60.13145846726431</v>
+        <v>59.59087533202102</v>
       </c>
       <c r="E92">
-        <v>119.6</v>
+        <v>123.4</v>
       </c>
       <c r="F92">
-        <v>342</v>
+        <v>345.8</v>
       </c>
       <c r="G92">
         <v>89.59999999999999</v>
@@ -8825,37 +8825,37 @@
         <v>18.6</v>
       </c>
       <c r="M92">
-        <v>80.64360000000001</v>
+        <v>81.53964000000001</v>
       </c>
       <c r="N92">
-        <v>-62.0436</v>
+        <v>-62.93964</v>
       </c>
       <c r="O92">
-        <v>-13.649592</v>
+        <v>-13.8467208</v>
       </c>
       <c r="P92">
-        <v>-48.394008</v>
+        <v>-49.0929192</v>
       </c>
       <c r="Q92">
-        <v>-15.494008</v>
+        <v>-16.19291920000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5379384350348803</v>
+        <v>0.5926204833720891</v>
       </c>
       <c r="T92">
-        <v>11.36578371905035</v>
+        <v>12.62864857672261</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05074178236090651</v>
+        <v>0.0501841803569405</v>
       </c>
       <c r="W92">
-        <v>0.2238350877192982</v>
+        <v>0.2239665702718334</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2306444652768478</v>
+        <v>0.2281099107133659</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2571454224508565</v>
+        <v>0.2590454224508564</v>
       </c>
       <c r="C93">
-        <v>-196.609124667979</v>
+        <v>-200.9400746964934</v>
       </c>
       <c r="D93">
-        <v>59.59087533202102</v>
+        <v>59.05992530350667</v>
       </c>
       <c r="E93">
-        <v>123.4</v>
+        <v>127.2</v>
       </c>
       <c r="F93">
-        <v>345.8</v>
+        <v>349.6</v>
       </c>
       <c r="G93">
         <v>89.59999999999999</v>
@@ -8907,37 +8907,37 @@
         <v>18.6</v>
       </c>
       <c r="M93">
-        <v>81.53964000000001</v>
+        <v>82.43568</v>
       </c>
       <c r="N93">
-        <v>-62.93964</v>
+        <v>-63.83568</v>
       </c>
       <c r="O93">
-        <v>-13.8467208</v>
+        <v>-14.0438496</v>
       </c>
       <c r="P93">
-        <v>-49.0929192</v>
+        <v>-49.7918304</v>
       </c>
       <c r="Q93">
-        <v>-16.19291920000001</v>
+        <v>-16.8918304</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5926204833720891</v>
+        <v>0.6609730437936004</v>
       </c>
       <c r="T93">
-        <v>12.62864857672261</v>
+        <v>14.20722964881294</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0501841803569405</v>
+        <v>0.04963870013566941</v>
       </c>
       <c r="W93">
-        <v>0.2239665702718334</v>
+        <v>0.2240951945080092</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2281099107133659</v>
+        <v>0.2256304551621336</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2590454224508564</v>
+        <v>0.2609454224508564</v>
       </c>
       <c r="C94">
-        <v>-200.9400746964934</v>
+        <v>-205.2616468349956</v>
       </c>
       <c r="D94">
-        <v>59.05992530350667</v>
+        <v>58.53835316500442</v>
       </c>
       <c r="E94">
-        <v>127.2</v>
+        <v>131.0000000000001</v>
       </c>
       <c r="F94">
-        <v>349.6</v>
+        <v>353.4</v>
       </c>
       <c r="G94">
         <v>89.59999999999999</v>
@@ -8989,37 +8989,37 @@
         <v>18.6</v>
       </c>
       <c r="M94">
-        <v>82.43568</v>
+        <v>83.33172000000002</v>
       </c>
       <c r="N94">
-        <v>-63.83568</v>
+        <v>-64.73172000000002</v>
       </c>
       <c r="O94">
-        <v>-14.0438496</v>
+        <v>-14.2409784</v>
       </c>
       <c r="P94">
-        <v>-49.7918304</v>
+        <v>-50.49074160000002</v>
       </c>
       <c r="Q94">
-        <v>-16.8918304</v>
+        <v>-17.59074160000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6609730437936004</v>
+        <v>0.7488549071926863</v>
       </c>
       <c r="T94">
-        <v>14.20722964881294</v>
+        <v>16.23683388435765</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04963870013566941</v>
+        <v>0.049104950671845</v>
       </c>
       <c r="W94">
-        <v>0.2240951945080092</v>
+        <v>0.224221052631579</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2256304551621336</v>
+        <v>0.223204321235659</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2609454224508564</v>
+        <v>0.2628454224508565</v>
       </c>
       <c r="C95">
-        <v>-205.2616468349956</v>
+        <v>-209.5740873636075</v>
       </c>
       <c r="D95">
-        <v>58.53835316500442</v>
+        <v>58.02591263639252</v>
       </c>
       <c r="E95">
-        <v>131.0000000000001</v>
+        <v>134.8000000000001</v>
       </c>
       <c r="F95">
-        <v>353.4</v>
+        <v>357.2</v>
       </c>
       <c r="G95">
         <v>89.59999999999999</v>
@@ -9071,37 +9071,37 @@
         <v>18.6</v>
       </c>
       <c r="M95">
-        <v>83.33172000000002</v>
+        <v>84.22776000000002</v>
       </c>
       <c r="N95">
-        <v>-64.73172000000002</v>
+        <v>-65.62776000000002</v>
       </c>
       <c r="O95">
-        <v>-14.2409784</v>
+        <v>-14.4381072</v>
       </c>
       <c r="P95">
-        <v>-50.49074160000002</v>
+        <v>-51.18965280000002</v>
       </c>
       <c r="Q95">
-        <v>-17.59074160000002</v>
+        <v>-18.28965280000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7488549071926863</v>
+        <v>0.8660307250581343</v>
       </c>
       <c r="T95">
-        <v>16.23683388435765</v>
+        <v>18.94297286508393</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.049104950671845</v>
+        <v>0.04858255757959133</v>
       </c>
       <c r="W95">
-        <v>0.224221052631579</v>
+        <v>0.2243442329227324</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.223204321235659</v>
+        <v>0.2208298071799605</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2628454224508565</v>
+        <v>0.2647454224508564</v>
       </c>
       <c r="C96">
-        <v>-209.5740873636075</v>
+        <v>-213.8776340136129</v>
       </c>
       <c r="D96">
-        <v>58.02591263639252</v>
+        <v>57.52236598638712</v>
       </c>
       <c r="E96">
-        <v>134.8000000000001</v>
+        <v>138.6</v>
       </c>
       <c r="F96">
-        <v>357.2</v>
+        <v>361</v>
       </c>
       <c r="G96">
         <v>89.59999999999999</v>
@@ -9153,37 +9153,37 @@
         <v>18.6</v>
       </c>
       <c r="M96">
-        <v>84.22776000000002</v>
+        <v>85.1238</v>
       </c>
       <c r="N96">
-        <v>-65.62776000000002</v>
+        <v>-66.52379999999999</v>
       </c>
       <c r="O96">
-        <v>-14.4381072</v>
+        <v>-14.635236</v>
       </c>
       <c r="P96">
-        <v>-51.18965280000002</v>
+        <v>-51.888564</v>
       </c>
       <c r="Q96">
-        <v>-18.28965280000002</v>
+        <v>-18.988564</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8660307250581343</v>
+        <v>1.030076870069762</v>
       </c>
       <c r="T96">
-        <v>18.94297286508393</v>
+        <v>22.73156743810073</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04858255757959133</v>
+        <v>0.04807116223664827</v>
       </c>
       <c r="W96">
-        <v>0.2243442329227324</v>
+        <v>0.2244648199445983</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2208298071799605</v>
+        <v>0.2185052828938558</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2647454224508564</v>
+        <v>0.2666454224508564</v>
       </c>
       <c r="C97">
-        <v>-213.8776340136129</v>
+        <v>-218.172516335199</v>
       </c>
       <c r="D97">
-        <v>57.52236598638712</v>
+        <v>57.02748366480107</v>
       </c>
       <c r="E97">
-        <v>138.6</v>
+        <v>142.4</v>
       </c>
       <c r="F97">
-        <v>361</v>
+        <v>364.8</v>
       </c>
       <c r="G97">
         <v>89.59999999999999</v>
@@ -9235,37 +9235,37 @@
         <v>18.6</v>
       </c>
       <c r="M97">
-        <v>85.1238</v>
+        <v>86.01984</v>
       </c>
       <c r="N97">
-        <v>-66.52379999999999</v>
+        <v>-67.41983999999999</v>
       </c>
       <c r="O97">
-        <v>-14.635236</v>
+        <v>-14.8323648</v>
       </c>
       <c r="P97">
-        <v>-51.888564</v>
+        <v>-52.58747519999999</v>
       </c>
       <c r="Q97">
-        <v>-18.988564</v>
+        <v>-19.68747519999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.030076870069762</v>
+        <v>1.276146087587203</v>
       </c>
       <c r="T97">
-        <v>22.73156743810073</v>
+        <v>28.41445929762592</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04807116223664827</v>
+        <v>0.04757042096334985</v>
       </c>
       <c r="W97">
-        <v>0.2244648199445983</v>
+        <v>0.2245828947368421</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2185052828938558</v>
+        <v>0.2162291861970449</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2666454224508564</v>
+        <v>0.2685454224508564</v>
       </c>
       <c r="C98">
-        <v>-218.172516335199</v>
+        <v>-222.4589560463765</v>
       </c>
       <c r="D98">
-        <v>57.02748366480107</v>
+        <v>56.54104395362349</v>
       </c>
       <c r="E98">
-        <v>142.4</v>
+        <v>146.2</v>
       </c>
       <c r="F98">
-        <v>364.8</v>
+        <v>368.6</v>
       </c>
       <c r="G98">
         <v>89.59999999999999</v>
@@ -9317,37 +9317,37 @@
         <v>18.6</v>
       </c>
       <c r="M98">
-        <v>86.01984</v>
+        <v>86.91588</v>
       </c>
       <c r="N98">
-        <v>-67.41983999999999</v>
+        <v>-68.31587999999999</v>
       </c>
       <c r="O98">
-        <v>-14.8323648</v>
+        <v>-15.0294936</v>
       </c>
       <c r="P98">
-        <v>-52.58747519999999</v>
+        <v>-53.2863864</v>
       </c>
       <c r="Q98">
-        <v>-19.68747519999999</v>
+        <v>-20.3863864</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.276146087587199</v>
+        <v>1.686261450116266</v>
       </c>
       <c r="T98">
-        <v>28.41445929762585</v>
+        <v>37.8859457301678</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04757042096334985</v>
+        <v>0.04708000425238748</v>
       </c>
       <c r="W98">
-        <v>0.2245828947368421</v>
+        <v>0.224698534997287</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2162291861970449</v>
+        <v>0.2140000193290341</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2685454224508564</v>
+        <v>0.2704454224508565</v>
       </c>
       <c r="C99">
-        <v>-222.4589560463765</v>
+        <v>-226.737167364194</v>
       </c>
       <c r="D99">
-        <v>56.54104395362349</v>
+        <v>56.06283263580601</v>
       </c>
       <c r="E99">
-        <v>146.2</v>
+        <v>150</v>
       </c>
       <c r="F99">
-        <v>368.6</v>
+        <v>372.4</v>
       </c>
       <c r="G99">
         <v>89.59999999999999</v>
@@ -9399,37 +9399,37 @@
         <v>18.6</v>
       </c>
       <c r="M99">
-        <v>86.91588</v>
+        <v>87.81192</v>
       </c>
       <c r="N99">
-        <v>-68.31587999999999</v>
+        <v>-69.21191999999999</v>
       </c>
       <c r="O99">
-        <v>-15.0294936</v>
+        <v>-15.2266224</v>
       </c>
       <c r="P99">
-        <v>-53.2863864</v>
+        <v>-53.9852976</v>
       </c>
       <c r="Q99">
-        <v>-20.3863864</v>
+        <v>-21.0852976</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.686261450116266</v>
+        <v>2.506492175174398</v>
       </c>
       <c r="T99">
-        <v>37.8859457301678</v>
+        <v>56.82891859525169</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04708000425238748</v>
+        <v>0.04659959604573047</v>
       </c>
       <c r="W99">
-        <v>0.224698534997287</v>
+        <v>0.2248118152524168</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2140000193290341</v>
+        <v>0.2118163456624113</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2704454224508565</v>
+        <v>0.2723454224508564</v>
       </c>
       <c r="C100">
-        <v>-226.737167364194</v>
+        <v>-231.007357319284</v>
       </c>
       <c r="D100">
-        <v>56.06283263580601</v>
+        <v>55.59264268071596</v>
       </c>
       <c r="E100">
-        <v>150</v>
+        <v>153.8</v>
       </c>
       <c r="F100">
-        <v>372.4</v>
+        <v>376.2</v>
       </c>
       <c r="G100">
         <v>89.59999999999999</v>
@@ -9481,37 +9481,37 @@
         <v>18.6</v>
       </c>
       <c r="M100">
-        <v>87.81192</v>
+        <v>88.70796</v>
       </c>
       <c r="N100">
-        <v>-69.21191999999999</v>
+        <v>-70.10795999999999</v>
       </c>
       <c r="O100">
-        <v>-15.2266224</v>
+        <v>-15.4237512</v>
       </c>
       <c r="P100">
-        <v>-53.9852976</v>
+        <v>-54.68420879999999</v>
       </c>
       <c r="Q100">
-        <v>-21.0852976</v>
+        <v>-21.78420879999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.506492175174398</v>
+        <v>4.967184350348797</v>
       </c>
       <c r="T100">
-        <v>56.82891859525169</v>
+        <v>113.6578371905034</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04659959604573047</v>
+        <v>0.04612889305536955</v>
       </c>
       <c r="W100">
-        <v>0.2248118152524168</v>
+        <v>0.2249228070175439</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2118163456624113</v>
+        <v>0.2096767866153162</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2723454224508564</v>
-      </c>
-      <c r="C101">
-        <v>-231.007357319284</v>
-      </c>
-      <c r="D101">
-        <v>55.59264268071596</v>
-      </c>
-      <c r="E101">
-        <v>153.8</v>
-      </c>
-      <c r="F101">
-        <v>376.2</v>
-      </c>
-      <c r="G101">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="H101">
-        <v>157.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>51.5</v>
-      </c>
-      <c r="K101">
-        <v>32.9</v>
-      </c>
-      <c r="L101">
-        <v>18.6</v>
-      </c>
-      <c r="M101">
-        <v>88.70796</v>
-      </c>
-      <c r="N101">
-        <v>-70.10795999999999</v>
-      </c>
-      <c r="O101">
-        <v>-15.4237512</v>
-      </c>
-      <c r="P101">
-        <v>-54.68420879999999</v>
-      </c>
-      <c r="Q101">
-        <v>-21.78420879999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.967184350348797</v>
-      </c>
-      <c r="T101">
-        <v>113.6578371905034</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04612889305536955</v>
-      </c>
-      <c r="W101">
-        <v>0.2249228070175439</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2096767866153162</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
